--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule &amp; Tranches" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Metrics &amp; Ratios" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside Stress &amp; Recovery" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earnings Deck &amp; Guidance" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +223,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6015,4 +6019,377 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="87" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Zorlu Enerji (ZOREN) — Earnings Presentation &amp; Management Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Source: Zorlu Enerji FY2024 Strategic Investor Presentation &amp; Capital Markets Day Deck | Reporting Currency: USD / Local Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>I. MANAGEMENT GUIDANCE &amp; STRATEGIC POLICY TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Strategic Guidance Metric</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Management Target / Commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Contracted Ebitda Share</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>&gt; 90.0% contracted under long-term take-or-pay Power Purchase Agreements (PPAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Net Debt Ebitda Target</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>&lt; 4.5x - 5.0x at consolidated level (&lt; 1.5x at corporate parent level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Portfolio Growth Capacity</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>+12.0% annual expansion in contracted generation gigawatts (GW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Green Energy Target</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>50.0%+ renewable solar and wind share in total capacity by 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>II. CAPITAL ALLOCATION &amp; STRATEGIC PROJECT PIPELINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Project / Capital Dimension</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Execution Milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Flagship Projects Under Construction</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Utility-Scale Solar PV Complexes, Combined-Cycle Gas Turbines &amp; Desalination Plants</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Capital Expenditure Envelope</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>$392.0M committed equity and project debt capex over 2025-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Project Financing Structure</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>75% - 80% non-recourse project debt ring-fenced at asset-level SPVs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Weighted Average Ppa Life</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>24.5 years with sovereign and investment grade national grid offtakers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>III. GEOGRAPHIC &amp; CURRENCY EXPOSURE MATRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Exposure Category</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Contractual / Balance Sheet Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Usd Denominated Tariffs</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>88.0% of PPA revenues denominated in or pegged to US Dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Sovereign Guarantee Backing</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>100.0% of offtake payment obligations guaranteed by national ministries of finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Inflation Indexation</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Tariffs feature contractual pass-through clauses for fuel price and local inflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>IV. CONTRACT BACKLOG &amp; COMMERCIAL MOAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Commercial / Asset Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Contracted Revenue Backlog</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>$21600.0M lifetime contractual revenue commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Equivalent Availability Factor</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>94.2% operational plant availability across generating fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Offtaker Counterparty Risk</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>Investment Grade (A/BBB) sovereign utility offtakers with zero historical defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>V. LIQUIDITY WATERFALL &amp; HEADROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Component</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Available Buffer / Runway</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Unrestricted Cash And Equivalents</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>$240.0M across corporate accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Undrawn Revolving Credit Facilities</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>$713.0M in multi-currency syndicated credit lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Liquidity Runway</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>38 months of corporate debt service and equity investment commitments fully secured</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C27:I27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,14 +215,35 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -4333,19 +4354,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="97" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
+    <col width="169" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -5119,9 +5140,551 @@
         <v>142.6</v>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>V. TRANCHE-BY-TRANCHE CAPITAL STRUCTURE &amp; PRICING DETAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Tranche / Instrument Name</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Instrument Type</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Ccy</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Amount Outstanding ($M)</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Coupon / Margin</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Clean Price</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>YTM (%)</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Seniority / Security</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Governing Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>ZOREN Benchmark Senior Notes</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured RegS/144A Eurobond</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>802.1</v>
+      </c>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>11.200%</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured (Pari Passu)</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>ZOREN Secondary Eurobond / Sukuk Tranche 2</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured Notes</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>534.7</v>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>10.550%</t>
+        </is>
+      </c>
+      <c r="G38" s="28" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Syndicated Commercial Bank Term Facility</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Senior Secured / Priority Amortizing Loan</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>USD / EUR</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>267.4</v>
+      </c>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>SOFR + 185 bps</t>
+        </is>
+      </c>
+      <c r="G39" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Senior Secured</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Drawn Revolving Credit Facility (RCF) &amp; Bilateral Lines</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Revolving Working Capital Credit Line</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>SOFR + 150 bps</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured (Pari Passu with Bonds)</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>VI. REVOLVING CREDIT FACILITY (RCF) &amp; BANK LIQUIDITY RUNWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Facility Designation</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>ZOREN Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Total Committed Capacity ($M)</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>499.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Drawn Amount ($M)</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>178.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>320.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Drawn Borrowing Margin</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>SOFR + 150 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Undrawn Commitment Fee</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>52.5 bps (35% of drawn margin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Maturity Date &amp; Extension Options</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>2028-06-30 (with two 1-year extension options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Syndicate Lenders / Arrangers</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>12 tier-1 international banks (Citi, HSBC, J.P. Morgan, Standard Chartered, FAB, BNP Paribas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>RCF Maintenance Covenants</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Tested semi-annually: Max 3.75x Net Debt / EBITDA, Min 3.0x EBITDA / Net Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>VII. BOND COVENANT ANALYSIS &amp; HEADROOM SCORECARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Covenant Test / Negative Pledge Dimension</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Governing Threshold / Limit</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Actual Current / Reported Metric</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Headroom / Compliance Status</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Covenant Terms / Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>4.50x</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>4.82x</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>-0.32x leverage buffer ($-102.4M EBITDA headroom)</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>Incurrence covenant for additional senior debt issuance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>2.50x</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>2.12x</t>
+        </is>
+      </c>
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>+-0.38x interest coverage cushion</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>Maintenance / incurrence gateway test</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Maximum Permitted Priority / Secured Debt</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>15.0% of Consolidated Total Tangible Assets</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="inlineStr">
+        <is>
+          <t>12.4% of Assets</t>
+        </is>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>$264.0M unutilized secured debt capacity</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>Permitted collateral carve-out limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Change of Control Put Option</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>101.00% Redemption</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Inactive)</t>
+        </is>
+      </c>
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>Investor Put Option at 101.00% of par upon Change of Control trigger accompanied by a Rating Downgrade below Investment Grade (or 1 notch drop if HY) within 90 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Restricted Payments / Dividend Basket</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>Builder Basket</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>Within Capacity</t>
+        </is>
+      </c>
+      <c r="E59" s="31" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>50.0% Cumulative Consolidated Net Income builder basket + $100M general starter basket; gated by minimum 2.50x Fixed Charge Coverage Ratio gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Default &amp; Cross-Acceleration</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>$50.0M threshold triggering cross-acceleration across all senior Eurobonds and syndicated loans.</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>Zero Defaults</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Cross-acceleration across all indebtedness exceeding threshold</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="16">
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="C43:F43"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5250,31 +5813,31 @@
           <t>NET LEVERAGE (Net Debt / EBITDA)</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="32">
         <f>'Debt Schedule &amp; Tranches'!C26 / 'Income Statement (P&amp;L)'!C22</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="32">
         <f>'Debt Schedule &amp; Tranches'!D26 / 'Income Statement (P&amp;L)'!D22</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="32">
         <f>'Debt Schedule &amp; Tranches'!E26 / 'Income Statement (P&amp;L)'!E22</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="32">
         <f>'Debt Schedule &amp; Tranches'!F26 / 'Income Statement (P&amp;L)'!F22</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="32">
         <f>'Debt Schedule &amp; Tranches'!G26 / 'Income Statement (P&amp;L)'!G22</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="32">
         <f>'Debt Schedule &amp; Tranches'!H26 / 'Income Statement (P&amp;L)'!H22</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="32">
         <f>'Debt Schedule &amp; Tranches'!I26 / 'Income Statement (P&amp;L)'!I22</f>
         <v/>
       </c>
@@ -5320,31 +5883,31 @@
           <t>EBITDA INTEREST COVERAGE</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="32">
         <f>'Income Statement (P&amp;L)'!C22 / 'Debt Schedule &amp; Tranches'!C28</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="32">
         <f>'Income Statement (P&amp;L)'!D22 / 'Debt Schedule &amp; Tranches'!D28</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="32">
         <f>'Income Statement (P&amp;L)'!E22 / 'Debt Schedule &amp; Tranches'!E28</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="32">
         <f>'Income Statement (P&amp;L)'!F22 / 'Debt Schedule &amp; Tranches'!F28</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="32">
         <f>'Income Statement (P&amp;L)'!G22 / 'Debt Schedule &amp; Tranches'!G28</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="32">
         <f>'Income Statement (P&amp;L)'!H22 / 'Debt Schedule &amp; Tranches'!H28</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="32">
         <f>'Income Statement (P&amp;L)'!I22 / 'Debt Schedule &amp; Tranches'!I28</f>
         <v/>
       </c>
@@ -5692,32 +6255,32 @@
           <t>Base Case (Consensus Forecast)</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>0 bp</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>11.20%</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>4.2x</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>$95.00</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>+0.5%</t>
         </is>
@@ -5729,32 +6292,32 @@
           <t>Downside Stress Case (Recession)</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>-15.0%</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>-300 bp</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>13.20%</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>3.2x</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>$76.50</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>-19.0%</t>
         </is>
@@ -5766,32 +6329,32 @@
           <t>Severe Distressed Floor (Liquidation)</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>-35.0%</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>-650 bp</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>+500 bp spread</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>Liquidation Value</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>$58.00</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>-38.6%</t>
         </is>
@@ -5803,32 +6366,32 @@
           <t>Bull Case (Cycle Peak / Accretion)</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>+12.0%</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>+200 bp</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>9.70%</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>5.7x</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>$105.00</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>+11.1%</t>
         </is>
@@ -5894,12 +6457,12 @@
           <t>First Lien Fixed Charges</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -5924,12 +6487,12 @@
           <t>General Corporate Guarantee</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>58.0%</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>95.0%</t>
         </is>
@@ -5954,12 +6517,12 @@
           <t>Junior Unsecured Claim</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
@@ -5984,12 +6547,12 @@
           <t>Ordinary Shares</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>Residual Only</t>
         </is>
@@ -6027,15 +6590,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="87" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="87" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -6063,7 +6626,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>I. MANAGEMENT GUIDANCE &amp; STRATEGIC POLICY TARGETS</t>
+          <t>I. MANAGEMENT STRATEGIC GUIDANCE TRACKER &amp; VARIANCE ANALYSIS</t>
         </is>
       </c>
     </row>
@@ -6075,289 +6638,391 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Management Target / Commitment</t>
+          <t>Company Target / Commitment</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Current Run-Rate</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Tracking Status</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Guidance Variance Analysis &amp; Operational Commentary</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Contracted Ebitda Share</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>&gt; 90.0% contracted under long-term take-or-pay Power Purchase Agreements (PPAs)</t>
+          <t>2025E Full-Year Gross Revenue Target</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>$1296.0M (+8.0% YoY growth)</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>$1278.0M (+6.5% YoY)</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Commercial volumes and contract deliveries progressing in line with FY budget.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Net Debt Ebitda Target</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>&lt; 4.5x - 5.0x at consolidated level (&lt; 1.5x at corporate parent level)</t>
+          <t>2025E Consolidated EBITDA Target</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>$352.0M (27.2% margin)</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>$345.6M</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>Operating cost discipline and high capacity utilization protecting margin guidance.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Portfolio Growth Capacity</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>+12.0% annual expansion in contracted generation gigawatts (GW)</t>
+          <t>Long-Term Net Leverage Ceiling</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 4.00x Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>4.82x</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>Deleveraging on track with -0.32x buffer below covenant limit.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Green Energy Target</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>50.0%+ renewable solar and wind share in total capacity by 2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+          <t>2025E Strategic Capex Envelope</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>$117.6M (Maximum growth and sustaining envelope)</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>$108.2M committed</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>Phased capital deployment self-funded from operating cashflow with zero debt draw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Annual Dividend Payout Policy</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>30% - 40% payout of attributable net profit</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>35% payout policy maintained</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>Dividend fully covered 2.4x by organic Free Cash Flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>II. CAPITAL ALLOCATION &amp; STRATEGIC PROJECT PIPELINE</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Project / Capital Dimension</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Disclosure &amp; Execution Milestone</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Flagship Projects Under Construction</t>
-        </is>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Utility-Scale Solar PV Complexes, Combined-Cycle Gas Turbines &amp; Desalination Plants</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Capital Expenditure Envelope</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>$392.0M committed equity and project debt capex over 2025-2027</t>
+          <t>Flagship Projects Under Construction</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Utility-Scale Solar PV Complexes, Combined-Cycle Gas Turbines &amp; Desalination Plants</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Project Financing Structure</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>75% - 80% non-recourse project debt ring-fenced at asset-level SPVs</t>
+          <t>Capital Expenditure Envelope</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>$392.0M committed equity and project debt capex over 2025-2027</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
+          <t>Project Financing Structure</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>75% - 80% non-recourse project debt ring-fenced at asset-level SPVs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
           <t>Weighted Average Ppa Life</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>24.5 years with sovereign and investment grade national grid offtakers</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>III. GEOGRAPHIC &amp; CURRENCY EXPOSURE MATRIX</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Exposure Category</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Contractual / Balance Sheet Profile</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Usd Denominated Tariffs</t>
-        </is>
-      </c>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>88.0% of PPA revenues denominated in or pegged to US Dollars</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sovereign Guarantee Backing</t>
-        </is>
-      </c>
-      <c r="C22" s="29" t="inlineStr">
-        <is>
-          <t>100.0% of offtake payment obligations guaranteed by national ministries of finance</t>
+          <t>Usd Denominated Tariffs</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>88.0% of PPA revenues denominated in or pegged to US Dollars</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>Sovereign Guarantee Backing</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>100.0% of offtake payment obligations guaranteed by national ministries of finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t>Inflation Indexation</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>Tariffs feature contractual pass-through clauses for fuel price and local inflation</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>IV. CONTRACT BACKLOG &amp; COMMERCIAL MOAT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Commercial / Asset Metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Contracted Revenue Backlog</t>
-        </is>
-      </c>
-      <c r="C27" s="29" t="inlineStr">
-        <is>
-          <t>$21600.0M lifetime contractual revenue commitment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Equivalent Availability Factor</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>94.2% operational plant availability across generating fleet</t>
+          <t>Contracted Revenue Backlog</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>$21600.0M lifetime contractual revenue commitment</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
+          <t>Equivalent Availability Factor</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>94.2% operational plant availability across generating fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>Offtaker Counterparty Risk</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>Investment Grade (A/BBB) sovereign utility offtakers with zero historical defaults</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>V. LIQUIDITY WATERFALL &amp; HEADROOM</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Liquidity Component</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Available Buffer / Runway</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Unrestricted Cash And Equivalents</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>$240.0M across corporate accounts</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Undrawn Revolving Credit Facilities</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>$713.0M in multi-currency syndicated credit lines</t>
+          <t>Unrestricted Cash And Equivalents</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>$240.0M across corporate accounts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
+          <t>Undrawn Revolving Credit Facilities</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>$713.0M in multi-currency syndicated credit lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
           <t>Liquidity Runway</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>38 months of corporate debt service and equity investment commitments fully secured</t>
         </is>
@@ -6365,28 +7030,28 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
+    <mergeCell ref="F9:I9"/>
     <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C8:I8"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="C7:I7"/>
     <mergeCell ref="C28:I28"/>
-    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C18:I18"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F11:I11"/>
     <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C30:I30"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C33:I33"/>
+    <mergeCell ref="F10:I10"/>
     <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C20:I20"/>
     <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C10:I10"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="F8:I8"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="C27:I27"/>
   </mergeCells>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -80,7 +80,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +111,12 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -247,6 +253,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1283,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1361,310 +1370,562 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Gross Installed Capacity (MW)</t>
+          <t>Total Installed Power Capacity (MW)</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>4200</v>
+        <v>990</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>4500</v>
+        <v>1005</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>5100</v>
+        <v>1025</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>5800</v>
+        <v>1045</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>6400</v>
+        <v>1075</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>7100</v>
+        <v>1110</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>7800</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Net Power Generation (GWh)</t>
+          <t>Geothermal Installed Capacity (Kizildere/Alasehir) (MW)</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>16800</v>
+        <v>305</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18200</v>
+        <v>305</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>20500</v>
+        <v>305</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>23400</v>
+        <v>305</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>26000</v>
+        <v>320</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>29000</v>
+        <v>340</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>32000</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Equivalent Availability Factor (%)</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>95</v>
+          <t>Wind Capacity (Gokcedag/Osmaniye) (MW)</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Average Realized Tariff ($/MWh)</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>84</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>87</v>
+          <t>Hydroelectric Capacity (7 Plants) (MW)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Renewable Generation Share (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
+          <t>Gas Cogeneration &amp; Industrial Steam (MW)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>341</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>International Capacity (Dorad Israel / Pakistan) (MW)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>290</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Gross Net Electricity Generation (GWh)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>4120</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>4380</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>4920</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>5500</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>II. BUSINESS SEGMENT REVENUE BREAKDOWN (USD M)</t>
-        </is>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Geothermal Plant Capacity Factor (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Business Segment</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>2021A</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>2022A</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>2023A</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>2024A</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>2025E</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Blended YEKDEM Realized Dollar Tariff ($/MWh)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>112.5</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Long-Term Contracted PPA Generation</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>554.9</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>669.1</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>750.7</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>816</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>881.3</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>938.4</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>979.2</v>
+          <t>OEDAS Regulated Asset Base (RAB) ($M)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>530</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>590</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>650</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>710</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>770</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>830</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Regulated Power Distribution &amp; Grid</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>216.5</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>264</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>285.1</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>303.6</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>316.8</v>
+          <t>OEDAS Electricity Distributed Volume (GWh)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>8900</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>9200</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>9500</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Merchant &amp; Capacity Balancing Services</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>129.6</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="I17" s="8" t="n">
+          <t>ZES Active Public EV Fast-Charging Sockets (Sockets)</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>650</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>980</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>2350</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>2850</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Natural USD Cash Flow Hedge Ratio (%)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>II. BUSINESS SEGMENT REVENUE BREAKDOWN (USD M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Business Segment</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2021A</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Renewable Power Generation (YEKDEM USD-Guaranteed)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>507.8</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>552</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>596.2</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>634.8</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>662.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Regulated Electricity Distribution &amp; Retail (OEDAS/OEPSAS)</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>456</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>547.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Thermal Cogeneration &amp; International IPPs (Dorad/Pakistan)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>144</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="G25" s="8" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>172.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ZES EV Charging Network &amp; Energy Solutions</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Total Consolidated Revenue (Feeds P&amp;L)</t>
         </is>
       </c>
-      <c r="C18" s="16">
-        <f>SUM(C15:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="16">
-        <f>SUM(D15:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>SUM(E15:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>SUM(F15:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>SUM(G15:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="16">
-        <f>SUM(H15:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="16">
-        <f>SUM(I15:I17)</f>
+      <c r="C27" s="16">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="16">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="16">
+        <f>SUM(E23:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="16">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="16">
+        <f>SUM(G23:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>SUM(H23:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>SUM(I23:I26)</f>
         <v/>
       </c>
     </row>
@@ -1802,105 +2063,105 @@
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Long-Term Contracted PPA Generation</t>
+          <t xml:space="preserve">  Renewable Power Generation (YEKDEM USD-Guaranteed)</t>
         </is>
       </c>
       <c r="C7" s="8">
-        <f>'Operational Drivers &amp; Segments'!C15</f>
+        <f>'Operational Drivers &amp; Segments'!C23</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>'Operational Drivers &amp; Segments'!D15</f>
+        <f>'Operational Drivers &amp; Segments'!D23</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>'Operational Drivers &amp; Segments'!E15</f>
+        <f>'Operational Drivers &amp; Segments'!E23</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>'Operational Drivers &amp; Segments'!F15</f>
+        <f>'Operational Drivers &amp; Segments'!F23</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>'Operational Drivers &amp; Segments'!G15</f>
+        <f>'Operational Drivers &amp; Segments'!G23</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>'Operational Drivers &amp; Segments'!H15</f>
+        <f>'Operational Drivers &amp; Segments'!H23</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>'Operational Drivers &amp; Segments'!I15</f>
+        <f>'Operational Drivers &amp; Segments'!I23</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Regulated Power Distribution &amp; Grid</t>
+          <t xml:space="preserve">  Regulated Electricity Distribution &amp; Retail (OEDAS/OEPSAS)</t>
         </is>
       </c>
       <c r="C8" s="8">
-        <f>'Operational Drivers &amp; Segments'!C16</f>
+        <f>'Operational Drivers &amp; Segments'!C24</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>'Operational Drivers &amp; Segments'!D16</f>
+        <f>'Operational Drivers &amp; Segments'!D24</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>'Operational Drivers &amp; Segments'!E16</f>
+        <f>'Operational Drivers &amp; Segments'!E24</f>
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>'Operational Drivers &amp; Segments'!F16</f>
+        <f>'Operational Drivers &amp; Segments'!F24</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>'Operational Drivers &amp; Segments'!G16</f>
+        <f>'Operational Drivers &amp; Segments'!G24</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>'Operational Drivers &amp; Segments'!H16</f>
+        <f>'Operational Drivers &amp; Segments'!H24</f>
         <v/>
       </c>
       <c r="I8" s="8">
-        <f>'Operational Drivers &amp; Segments'!I16</f>
+        <f>'Operational Drivers &amp; Segments'!I24</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Merchant &amp; Capacity Balancing Services</t>
+          <t xml:space="preserve">  Thermal Cogeneration &amp; International IPPs (Dorad/Pakistan)</t>
         </is>
       </c>
       <c r="C9" s="8">
-        <f>'Operational Drivers &amp; Segments'!C17</f>
+        <f>'Operational Drivers &amp; Segments'!C25</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>'Operational Drivers &amp; Segments'!D17</f>
+        <f>'Operational Drivers &amp; Segments'!D25</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>'Operational Drivers &amp; Segments'!E17</f>
+        <f>'Operational Drivers &amp; Segments'!E25</f>
         <v/>
       </c>
       <c r="F9" s="8">
-        <f>'Operational Drivers &amp; Segments'!F17</f>
+        <f>'Operational Drivers &amp; Segments'!F25</f>
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>'Operational Drivers &amp; Segments'!G17</f>
+        <f>'Operational Drivers &amp; Segments'!G25</f>
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>'Operational Drivers &amp; Segments'!H17</f>
+        <f>'Operational Drivers &amp; Segments'!H25</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>'Operational Drivers &amp; Segments'!I17</f>
+        <f>'Operational Drivers &amp; Segments'!I25</f>
         <v/>
       </c>
     </row>
@@ -1911,31 +2172,31 @@
         </is>
       </c>
       <c r="C10" s="16">
-        <f>SUM(C7:C9)</f>
+        <f>SUM(C7:C10)</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>SUM(D7:D9)</f>
+        <f>SUM(D7:D10)</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>SUM(E7:E9)</f>
+        <f>SUM(E7:E10)</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>SUM(F7:F9)</f>
+        <f>SUM(F7:F10)</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>SUM(G7:G9)</f>
+        <f>SUM(G7:G10)</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>SUM(H7:H9)</f>
+        <f>SUM(H7:H10)</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>SUM(I7:I9)</f>
+        <f>SUM(I7:I10)</f>
         <v/>
       </c>
     </row>
@@ -4359,14 +4620,14 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="97" customWidth="1" min="3" max="3"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="53" customWidth="1" min="5" max="5"/>
     <col width="169" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="81" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -5199,7 +5460,7 @@
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>ZOREN Benchmark Senior Notes</t>
+          <t>ZOREN 9.000% Senior Notes Due 2026 (Eurobond)</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -5213,11 +5474,11 @@
         </is>
       </c>
       <c r="E37" s="21" t="n">
-        <v>802.1</v>
+        <v>300</v>
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>9.000%</t>
         </is>
       </c>
       <c r="G37" s="28" t="n">
@@ -5228,24 +5489,24 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured (Pari Passu)</t>
+          <t>Senior Unsecured (Pari Passu with Bank Debt)</t>
         </is>
       </c>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>English Law</t>
+          <t>English Law / Rule 144A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>ZOREN Secondary Eurobond / Sukuk Tranche 2</t>
+          <t>Kizildere &amp; Alasehir Geothermal Project Finance Facilities</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured Notes</t>
+          <t>Senior Secured Amortizing Project Finance Loans (EBRD / IFC / Commercial)</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
@@ -5254,109 +5515,109 @@
         </is>
       </c>
       <c r="E38" s="21" t="n">
-        <v>534.7</v>
+        <v>720</v>
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>10.550%</t>
+          <t>SOFR + 325 bps</t>
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="H38" s="29" t="n">
-        <v>10.55</v>
+        <v>8.15</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured</t>
+          <t>Senior Secured (First Lien on Geothermal Plant Assets &amp; YEKDEM Cash Accounts)</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>English Law</t>
+          <t>English Law / Turkish Security Documentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Syndicated Commercial Bank Term Facility</t>
+          <t>OEDAS Regulated Grid Distribution Investment Loans</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Senior Secured / Priority Amortizing Loan</t>
+          <t>Senior Secured Capex Facilities &amp; TLREF Bonds</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t>USD / EUR</t>
+          <t>TRY / EUR</t>
         </is>
       </c>
       <c r="E39" s="21" t="n">
-        <v>267.4</v>
+        <v>480</v>
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>SOFR + 185 bps</t>
+          <t>TLREF + 350 bps / Euribor + 275 bps</t>
         </is>
       </c>
       <c r="G39" s="28" t="n">
         <v>100</v>
       </c>
       <c r="H39" s="29" t="n">
-        <v>6.85</v>
+        <v>14.5</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Senior Secured</t>
+          <t>Senior Secured (Pledge on Regulated Tariff Receivables)</t>
         </is>
       </c>
       <c r="J39" s="17" t="inlineStr">
         <is>
-          <t>English Law</t>
+          <t>Turkish Law</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Drawn Revolving Credit Facility (RCF) &amp; Bilateral Lines</t>
+          <t>Zorlu Enerji Syndicated Multi-Currency RCF &amp; Bilateral Working Capital</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Revolving Working Capital Credit Line</t>
+          <t>Revolving Working Capital Credit Facilities</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD / EUR / TRY</t>
         </is>
       </c>
       <c r="E40" s="21" t="n">
-        <v>178.2</v>
+        <v>282.4</v>
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>SOFR + 150 bps</t>
+          <t>SOFR + 285 bps</t>
         </is>
       </c>
       <c r="G40" s="28" t="n">
         <v>100</v>
       </c>
       <c r="H40" s="29" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured (Pari Passu with Bonds)</t>
+          <t>Senior Unsecured (Pari Passu with Eurobonds)</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t>English Law</t>
+          <t>Turkish / English Law</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5637,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ZOREN Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
+          <t>Zorlu Enerji Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5648,7 @@
         </is>
       </c>
       <c r="C44" s="21" t="n">
-        <v>499.1</v>
+        <v>462.4</v>
       </c>
     </row>
     <row r="45">
@@ -5397,7 +5658,7 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>178.2</v>
+        <v>282.4</v>
       </c>
     </row>
     <row r="46">
@@ -5407,7 +5668,7 @@
         </is>
       </c>
       <c r="C46" s="20" t="n">
-        <v>320.9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47">
@@ -5418,7 +5679,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>SOFR + 150 bps</t>
+          <t>SOFR + 285 bps / Euribor + 250 bps</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5691,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>52.5 bps (35% of drawn margin)</t>
+          <t>75.0 bps</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5703,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>2028-06-30 (with two 1-year extension options)</t>
+          <t>2027-06-30 (with 1-year annual extension options)</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5715,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>12 tier-1 international banks (Citi, HSBC, J.P. Morgan, Standard Chartered, FAB, BNP Paribas)</t>
+          <t>Akbank, Garanti BBVA, Turkiye Is Bankasi, Vakifbank, QNB Finansbank</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5727,7 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Tested semi-annually: Max 3.75x Net Debt / EBITDA, Min 3.0x EBITDA / Net Interest</t>
+          <t>Semi-annual testing: Consolidated Net Debt / EBITDA &lt;= 5.0x, Minimum Interest Coverage &gt;= 2.0x</t>
         </is>
       </c>
     </row>
@@ -6590,15 +6851,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="87" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="231" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="87" customWidth="1" min="6" max="6"/>
+    <col width="150" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -6618,7 +6879,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Source: Zorlu Enerji FY2024 Strategic Investor Presentation &amp; Capital Markets Day Deck | Reporting Currency: USD / Local Currency</t>
+          <t>Source: Zorlu Enerji FY2024 Strategic Investor Presentation &amp; Borsa Istanbul Capital Markets Day | Reporting Currency: USD / TRY (with natural USD hedge disclosures)</t>
         </is>
       </c>
     </row>
@@ -6660,17 +6921,17 @@
     <row r="7">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2025E Full-Year Gross Revenue Target</t>
+          <t>2025E Full-Year Consolidated Revenue Target</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>$1296.0M (+8.0% YoY growth)</t>
+          <t>$1,280M - $1,320M (+8.0% YoY)</t>
         </is>
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>$1278.0M (+6.5% YoY)</t>
+          <t>$1,295M annualized (9M24 actuals)</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -6680,7 +6941,7 @@
       </c>
       <c r="F7" s="36" t="inlineStr">
         <is>
-          <t>Commercial volumes and contract deliveries progressing in line with FY budget.</t>
+          <t>High geothermal plant availability (88.5%) and steady OEDAS distribution volume (+3.8%) tracking in line with guidance envelope.</t>
         </is>
       </c>
     </row>
@@ -6692,12 +6953,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>$352.0M (27.2% margin)</t>
+          <t>$330M - $350M (26.5% - 27.5% margin)</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
         <is>
-          <t>$345.6M</t>
+          <t>$338M annualized run-rate</t>
         </is>
       </c>
       <c r="E8" s="35" t="inlineStr">
@@ -6707,51 +6968,51 @@
       </c>
       <c r="F8" s="36" t="inlineStr">
         <is>
-          <t>Operating cost discipline and high capacity utilization protecting margin guidance.</t>
+          <t>USD-denominated YEKDEM cash flows ($105-$132/MWh) generated 68.5% of generation EBITDA, protecting margins against TRY depreciation.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Long-Term Net Leverage Ceiling</t>
+          <t>Consolidated Net Leverage Ceiling</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>&lt; 4.00x Net Debt / EBITDA</t>
+          <t>&lt; 3.50x Net Debt / EBITDA</t>
         </is>
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>4.82x</t>
-        </is>
-      </c>
-      <c r="E9" s="35" t="inlineStr">
-        <is>
-          <t>On Track</t>
+          <t>4.82x Net Debt / EBITDA (2024A)</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Under Watch</t>
         </is>
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
-          <t>Deleveraging on track with -0.32x buffer below covenant limit.</t>
+          <t>Elevated leverage due to TRY translation of unhedged debt; deleveraging milestone contingent on executing Zorlu Yenilenebilir equity monetization.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2025E Strategic Capex Envelope</t>
+          <t>2025E Strategic Capex Discipline Envelope</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>$117.6M (Maximum growth and sustaining envelope)</t>
+          <t>&lt; $115.0M maximum capex envelope</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>$108.2M committed</t>
+          <t>$108.2M committed / incurred</t>
         </is>
       </c>
       <c r="E10" s="35" t="inlineStr">
@@ -6761,34 +7022,34 @@
       </c>
       <c r="F10" s="36" t="inlineStr">
         <is>
-          <t>Phased capital deployment self-funded from operating cashflow with zero debt draw.</t>
+          <t>Discretionary thermal capex frozen; capital deployed exclusively into regulated OEDAS grid capex (RAB-accretive) and Kizildere hybrid solar.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Annual Dividend Payout Policy</t>
+          <t>ZES Electric Vehicle Fast-Charging Sockets</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>30% - 40% payout of attributable net profit</t>
+          <t>2,200+ public sockets by end-2025</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>35% payout policy maintained</t>
-        </is>
-      </c>
-      <c r="E11" s="35" t="inlineStr">
-        <is>
-          <t>On Track</t>
+          <t>1,850 sockets active across 81 provinces</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Ahead of Target</t>
         </is>
       </c>
       <c r="F11" s="36" t="inlineStr">
         <is>
-          <t>Dividend fully covered 2.4x by organic Free Cash Flow.</t>
+          <t>Consolidated #1 market position in Turkey with 38% market share; Electrip international pilot expanding across Italy, France, and Poland.</t>
         </is>
       </c>
     </row>
@@ -6815,48 +7076,48 @@
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Flagship Projects Under Construction</t>
+          <t>Kizildere Hybrid Solar</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>Utility-Scale Solar PV Complexes, Combined-Cycle Gas Turbines &amp; Desalination Plants</t>
+          <t>50 MW co-located solar PV under construction at Kizildere to utilize existing transmission capacity and boost summer generation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Capital Expenditure Envelope</t>
+          <t>Alasehir Geothermal Expansion</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>$392.0M committed equity and project debt capex over 2025-2027</t>
+          <t>Preliminary drilling and resource appraisal for Alasehir II geothermal project (potential +30 MW expansion)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Project Financing Structure</t>
+          <t>Oedas Smart Grid Investments</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>75% - 80% non-recourse project debt ring-fenced at asset-level SPVs</t>
+          <t>TRY 3.8B committed grid modernization and digital substation automation under 4th Tariff Period</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Weighted Average Ppa Life</t>
+          <t>Zes Electrip Europe</t>
         </is>
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>24.5 years with sovereign and investment grade national grid offtakers</t>
+          <t>Targeting 500 ultra-fast DC charging hubs across Southern and Central Europe by 2026</t>
         </is>
       </c>
     </row>
@@ -6883,177 +7144,519 @@
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Usd Denominated Tariffs</t>
+          <t>Usd Revenue Share</t>
         </is>
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>88.0% of PPA revenues denominated in or pegged to US Dollars</t>
+          <t>68.5% of generation EBITDA earned in US Dollars directly under statutory YEKDEM mechanism</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Sovereign Guarantee Backing</t>
+          <t>Try Regulated Revenue Share</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>100.0% of offtake payment obligations guaranteed by national ministries of finance</t>
+          <t>31.5% of revenue earned in Turkish Lira via OEDAS/OEPSAS with full CPI inflation pass-through</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Inflation Indexation</t>
+          <t>Debt Currency Denomination</t>
         </is>
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>Tariffs feature contractual pass-through clauses for fuel price and local inflation</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+          <t>58% USD, 24% EUR, 18% TRY — natural dollar hedge covers 100% of USD net interest payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Fx Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Bilateral FX forward hedges covering next 12-month EUR debt principal amortizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>IV. CONTRACT BACKLOG &amp; COMMERCIAL MOAT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Commercial / Asset Metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Contracted Revenue Backlog</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="inlineStr">
-        <is>
-          <t>$21600.0M lifetime contractual revenue commitment</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Equivalent Availability Factor</t>
+          <t>Contracted Generation Capacity</t>
         </is>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>94.2% operational plant availability across generating fleet</t>
+          <t>643 MW operating under government-backed take-or-pay feed-in tariffs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Offtaker Counterparty Risk</t>
+          <t>Offtaker Counterparty</t>
         </is>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>Investment Grade (A/BBB) sovereign utility offtakers with zero historical defaults</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+          <t>Republic of Turkey Ministry of Energy and Natural Resources / EPIAS (100% sovereign-backed offtake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Average Concession Life</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>Distribution concession through 2036; Geothermal exploration licenses valid through 2041-2047</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>V. LIQUIDITY WATERFALL &amp; HEADROOM</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Liquidity Component</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Available Buffer / Runway</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Unrestricted Cash And Equivalents</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>$240.0M across corporate accounts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Undrawn Revolving Credit Facilities</t>
+          <t>Unrestricted Cash Reserves</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>$713.0M in multi-currency syndicated credit lines</t>
+          <t>$240.0M held in tier-1 commercial and state banks (Akbank, Garanti, Isbank)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Liquidity Runway</t>
+          <t>Undrawn Committed Facilities</t>
         </is>
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>38 months of corporate debt service and equity investment commitments fully secured</t>
+          <t>$180.0M undrawn revolving credit lines and overdraft limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Next 12M Debt Service</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>$260.0M scheduled amortization and coupon payments fully covered by internal operating cash flow ($272M CFO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>VI. GENERATION FLEET BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Operational Asset / Disclosure Dimension</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Investor Deck Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Geothermal Capacity Jes</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>305.0 MW total geothermal capacity: Kizildere I (15.0 MW), Kizildere II (80.0 MW), Kizildere III Unit 1 (99.5 MW), Kizildere III Unit 2 (65.5 MW), Alasehir I (45.0 MW) — Turkey's largest and lowest-cost baseload renewable fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Wind Capacity Res</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="inlineStr">
+        <is>
+          <t>135.0 MW Gokcedag Wind Power Plant (Osmaniye) — long-term high wind resource capacity factor (&gt;34%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Hydroelectric Capacity Hes</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>118.6 MW across 7 operating run-of-river and reservoir plants (Ikizdere, Atabey, Camlica, Kuzgun, Mercan, Tercan, Beykoy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Solar And Hybrid Capacity</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>84.0 MW installed and under development (hybrid solar installations co-located at Kizildere geothermal sites)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Thermal And Industrial Cogen</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>341.0 MW domestic gas cogeneration and district heating (Bursa, Luleburgaz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>International Power Assets</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>290.4 MW total international holdings: 56.4 MW Jhimpir Wind (Pakistan, sovereign USD PPA) + 25.0% equity interest in 840 MW Dorad Energy (Israel, 210 MW net share)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>VII. YEKDEM FEED IN TARIFF MECHANICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Operational Asset / Disclosure Dimension</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Investor Deck Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Geothermal Dollar Tariff</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>$105.0/MWh base feed-in tariff + up to $27.0/MWh domestic equipment component bonus = $132.0/MWh guaranteed in US Dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Wind Dollar Tariff</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>$73.0/MWh base tariff + up to $21.0/MWh local blade/tower manufacturing bonus = $94.0/MWh guaranteed in US Dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Dollar Natural Hedge Ratio</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>68.5% of total power generation cash EBITDA is received in hard currency US Dollars via YEKDEM settlement, fully covering annual USD debt service on project loans and Eurobonds</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Yekdem Contract Expiry Schedule</t>
+        </is>
+      </c>
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>Kizildere II active through 2026; Alasehir active through 2026; Kizildere III Unit 1 through 2028; Kizildere III Unit 2 through 2029; Gokcedag Wind through 2025 (transitioning to merchant/bilateral contracts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>VIII. DISTRIBUTION AND RETAIL OEDAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Operational Asset / Disclosure Dimension</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Investor Deck Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Concession Area</t>
+        </is>
+      </c>
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>Osmangazi electricity distribution region covering 5 provinces: Afyonkarahisar, Bilecik, Eskisehir, Kutahya, Usak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Customer Reach</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>1.95 million registered meters serving a regional population of ~2.9 million</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Annual Volume Distributed</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>8,650 GWh distributed electricity volume (+3.8% organic growth in 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Regulated Asset Base Rab</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>$650.0M equivalent (TRY 22.5B), earning a real pre-tax allowed return on equity (WACC) set by EMRA (12.3% real return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Inflation Protection</t>
+        </is>
+      </c>
+      <c r="C60" s="36" t="inlineStr">
+        <is>
+          <t>Distribution tariffs and opex/capex allowances are adjusted monthly for Turkish CPI/PPI, shielding real operating margin against currency depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>IX. ZES ELECTRIC VEHICLE CHARGING NETWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Operational Asset / Disclosure Dimension</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Investor Deck Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Active Charging Sockets</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>1,850+ public AC/DC fast-charging sockets operating across all 81 provinces of Turkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Market Share</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>~35% - 38% market share in public DC fast charging, maintaining clear #1 market leadership in Turkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>European Expansion Electrip</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="inlineStr">
+        <is>
+          <t>International EV charging rollout under the Electrip brand with active high-power hubs launched in Italy, France, Poland, Bulgaria, and Greece</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Charging Volume Growth</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>+78.0% YoY increase in electricity delivered via charging network (transitioning into high-margin recurring cash flow stream)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="48">
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C52:I52"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C48:I48"/>
+    <mergeCell ref="C39:I39"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="C37:I37"/>
     <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C66:I66"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C49:I49"/>
     <mergeCell ref="F11:I11"/>
     <mergeCell ref="C34:I34"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C42:I42"/>
     <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C33:I33"/>
     <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C58:I58"/>
     <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C45:I45"/>
     <mergeCell ref="F7:I7"/>
+    <mergeCell ref="C64:I64"/>
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="C29:I29"/>
     <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C63:I63"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="C65:I65"/>
+    <mergeCell ref="C55:I55"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C44:I44"/>
     <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C40:I40"/>
     <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C56:I56"/>
     <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="C43:I43"/>
+    <mergeCell ref="C60:I60"/>
+    <mergeCell ref="C51:I51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -333,6 +333,152 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CEMBI Credit Desk</author>
+  </authors>
+  <commentList>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2021A):
+Revenues supported by high baseload geothermal availability; early stages of TRY volatility.</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2022A):
+Top-line expanded +18.5% YoY to $980M as power demand and regional electricity consumption surged.</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2023A):
+Consolidated revenue reached $1,100M supported by OEDAS 4th tariff period indexation.</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2024A):
+Revenue achieved $1,200M (+9.1% YoY) anchored by 1.95M OEDAS customers and 305 MW geothermal baseload fleet.</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2025E):
+Forecast revenue of $1,296M (+8.0% YoY) reflecting high geothermal capacity factor (88.5%) and RAB growth.</t>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2026E):
+Revenue anticipated at $1,375M driven by expanded ZES EV charging network and growing regional power demand.</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2027E):
+Revenue reaches $1,440M with international power assets (Dorad Israel / Pakistan) contributing steady dividends.</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2021A):
+EBITDA margin of 27.2% anchored by Kizildere I/II YEKDEM dollar-denominated feed-in tariffs.</t>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2022A):
+EBITDA rose to $270M; YEKDEM dollar cash receipts ($105-$132/MWh) insulated generation profitability.</t>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2023A):
+EBITDA expanded to $295M; commercial operations of hybrid solar capacity provided peak summer revenue.</t>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2024A):
+EBITDA reached $320M; 68.5% of generation EBITDA earned in US Dollars directly under statutory YEKDEM.</t>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2025E):
+EBITDA projected at $352M (27.2% margin) supported by locked-in YEKDEM dollar tariffs.</t>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2026E):
+EBITDA reaches $378M; ZES fast-charging network transitions into a high-margin recurring cash flow contributor.</t>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Analyst Observation (2027E):
+EBITDA of $398M reflects mature low-cost baseload geothermal and wind generation infrastructure.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CEMBI Credit Desk</author>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2021A):
+Net leverage at 4.73x; unhedged foreign currency debt tracking Turkish Lira movements.</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2022A):
+Net leverage held at 4.80x despite TRY depreciation due to strong USD generation cash conversion.</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2023A):
+Net leverage stabilized at 4.75x; preliminary plans drafted for renewable subsidiary equity monetization.</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2024A):
+Net leverage at 4.82x (restricting debt incurrence covenant); management prioritizes de-leveraging to &lt;3.5x.</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2025E):
+Net leverage expected to decrease to 3.90x assisted by operating cash generation and targeted asset sales.</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2026E):
+Net leverage improves to 3.37x; covenant headroom restores fully across all bank facilities.</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Leverage Commentary (2027E):
+Net leverage falls to conservative 2.87x, positioning Zorlu Enerji for sovereign-ceiling rating upgrades.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2877,6 +3023,7 @@
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6431,6 +6578,7 @@
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,6 +215,15 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -232,9 +241,6 @@
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -423,6 +429,48 @@
 EBITDA of $398M reflects mature low-cost baseload geothermal and wind generation infrastructure.</t>
       </text>
     </comment>
+    <comment ref="C36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2021A):
+Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="D36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2022A):
+Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2023A):
+Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2024A):
+Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="G36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2025E):
+Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="H36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2026E):
+Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk EBITDA Audit (2027E):
+Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -435,44 +483,86 @@
   <commentList>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2021A):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2021A):
 Net leverage at 4.73x; unhedged foreign currency debt tracking Turkish Lira movements.</t>
       </text>
     </comment>
     <comment ref="D8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2022A):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2022A):
 Net leverage held at 4.80x despite TRY depreciation due to strong USD generation cash conversion.</t>
       </text>
     </comment>
     <comment ref="E8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2023A):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2023A):
 Net leverage stabilized at 4.75x; preliminary plans drafted for renewable subsidiary equity monetization.</t>
       </text>
     </comment>
     <comment ref="F8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2024A):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2024A):
 Net leverage at 4.82x (restricting debt incurrence covenant); management prioritizes de-leveraging to &lt;3.5x.</t>
       </text>
     </comment>
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2025E):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2025E):
 Net leverage expected to decrease to 3.90x assisted by operating cash generation and targeted asset sales.</t>
       </text>
     </comment>
     <comment ref="H8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2026E):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2026E):
 Net leverage improves to 3.37x; covenant headroom restores fully across all bank facilities.</t>
       </text>
     </comment>
     <comment ref="I8" authorId="0" shapeId="0">
       <text>
-        <t>CEMBI Credit Desk Leverage Commentary (2027E):
+        <t>CEMBI Credit Desk Calculated Leverage Commentary (2027E):
 Net leverage falls to conservative 2.87x, positioning Zorlu Enerji for sovereign-ceiling rating upgrades.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2021A):
+Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2022A):
+Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2023A):
+Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2024A):
+Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2025E):
+Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2026E):
+Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk Reported Leverage Commentary (2027E):
+Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
       </text>
     </comment>
   </commentList>
@@ -904,7 +994,7 @@
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Calculated Cash EBITDA</t>
         </is>
       </c>
       <c r="C12" s="8">
@@ -939,320 +1029,388 @@
     <row r="13">
       <c r="B13" s="9" t="inlineStr">
         <is>
+          <t>Reported Headline EBITDA</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>'Income Statement (P&amp;L)'!C36</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>'Income Statement (P&amp;L)'!D36</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>'Income Statement (P&amp;L)'!E36</f>
+        <v/>
+      </c>
+      <c r="F13" s="8">
+        <f>'Income Statement (P&amp;L)'!F36</f>
+        <v/>
+      </c>
+      <c r="G13" s="8">
+        <f>'Income Statement (P&amp;L)'!G36</f>
+        <v/>
+      </c>
+      <c r="H13" s="8">
+        <f>'Income Statement (P&amp;L)'!H36</f>
+        <v/>
+      </c>
+      <c r="I13" s="8">
+        <f>'Income Statement (P&amp;L)'!I36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
           <t>EBITDA Margin (%)</t>
         </is>
       </c>
-      <c r="C13" s="10">
+      <c r="C14" s="10">
         <f>'Income Statement (P&amp;L)'!C23</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D14" s="10">
         <f>'Income Statement (P&amp;L)'!D23</f>
         <v/>
       </c>
-      <c r="E13" s="10">
+      <c r="E14" s="10">
         <f>'Income Statement (P&amp;L)'!E23</f>
         <v/>
       </c>
-      <c r="F13" s="10">
+      <c r="F14" s="10">
         <f>'Income Statement (P&amp;L)'!F23</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G14" s="10">
         <f>'Income Statement (P&amp;L)'!G23</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H14" s="10">
         <f>'Income Statement (P&amp;L)'!H23</f>
         <v/>
       </c>
-      <c r="I13" s="10">
+      <c r="I14" s="10">
         <f>'Income Statement (P&amp;L)'!I23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Cash Flow from Operations (CFO)</t>
-        </is>
-      </c>
-      <c r="C14" s="8">
-        <f>'Cash Flow Statement'!C14</f>
-        <v/>
-      </c>
-      <c r="D14" s="8">
-        <f>'Cash Flow Statement'!D14</f>
-        <v/>
-      </c>
-      <c r="E14" s="8">
-        <f>'Cash Flow Statement'!E14</f>
-        <v/>
-      </c>
-      <c r="F14" s="8">
-        <f>'Cash Flow Statement'!F14</f>
-        <v/>
-      </c>
-      <c r="G14" s="8">
-        <f>'Cash Flow Statement'!G14</f>
-        <v/>
-      </c>
-      <c r="H14" s="8">
-        <f>'Cash Flow Statement'!H14</f>
-        <v/>
-      </c>
-      <c r="I14" s="8">
-        <f>'Cash Flow Statement'!I14</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Capital Expenditures (Capex)</t>
+          <t>Cash Flow from Operations (CFO)</t>
         </is>
       </c>
       <c r="C15" s="8">
-        <f>'Cash Flow Statement'!C16</f>
+        <f>'Cash Flow Statement'!C14</f>
         <v/>
       </c>
       <c r="D15" s="8">
-        <f>'Cash Flow Statement'!D16</f>
+        <f>'Cash Flow Statement'!D14</f>
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>'Cash Flow Statement'!E16</f>
+        <f>'Cash Flow Statement'!E14</f>
         <v/>
       </c>
       <c r="F15" s="8">
-        <f>'Cash Flow Statement'!F16</f>
+        <f>'Cash Flow Statement'!F14</f>
         <v/>
       </c>
       <c r="G15" s="8">
-        <f>'Cash Flow Statement'!G16</f>
+        <f>'Cash Flow Statement'!G14</f>
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>'Cash Flow Statement'!H16</f>
+        <f>'Cash Flow Statement'!H14</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>'Cash Flow Statement'!I16</f>
+        <f>'Cash Flow Statement'!I14</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Free Cash Flow (FCF)</t>
+          <t>Capital Expenditures (Capex)</t>
         </is>
       </c>
       <c r="C16" s="8">
-        <f>'Cash Flow Statement'!C26</f>
+        <f>'Cash Flow Statement'!C16</f>
         <v/>
       </c>
       <c r="D16" s="8">
-        <f>'Cash Flow Statement'!D26</f>
+        <f>'Cash Flow Statement'!D16</f>
         <v/>
       </c>
       <c r="E16" s="8">
-        <f>'Cash Flow Statement'!E26</f>
+        <f>'Cash Flow Statement'!E16</f>
         <v/>
       </c>
       <c r="F16" s="8">
-        <f>'Cash Flow Statement'!F26</f>
+        <f>'Cash Flow Statement'!F16</f>
         <v/>
       </c>
       <c r="G16" s="8">
-        <f>'Cash Flow Statement'!G26</f>
+        <f>'Cash Flow Statement'!G16</f>
         <v/>
       </c>
       <c r="H16" s="8">
-        <f>'Cash Flow Statement'!H26</f>
+        <f>'Cash Flow Statement'!H16</f>
         <v/>
       </c>
       <c r="I16" s="8">
-        <f>'Cash Flow Statement'!I26</f>
+        <f>'Cash Flow Statement'!I16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Cash &amp; Liquid Reserves</t>
+          <t>Free Cash Flow (FCF)</t>
         </is>
       </c>
       <c r="C17" s="8">
-        <f>'Balance Sheet'!C8</f>
+        <f>'Cash Flow Statement'!C26</f>
         <v/>
       </c>
       <c r="D17" s="8">
-        <f>'Balance Sheet'!D8</f>
+        <f>'Cash Flow Statement'!D26</f>
         <v/>
       </c>
       <c r="E17" s="8">
-        <f>'Balance Sheet'!E8</f>
+        <f>'Cash Flow Statement'!E26</f>
         <v/>
       </c>
       <c r="F17" s="8">
-        <f>'Balance Sheet'!F8</f>
+        <f>'Cash Flow Statement'!F26</f>
         <v/>
       </c>
       <c r="G17" s="8">
-        <f>'Balance Sheet'!G8</f>
+        <f>'Cash Flow Statement'!G26</f>
         <v/>
       </c>
       <c r="H17" s="8">
-        <f>'Balance Sheet'!H8</f>
+        <f>'Cash Flow Statement'!H26</f>
         <v/>
       </c>
       <c r="I17" s="8">
-        <f>'Balance Sheet'!I8</f>
+        <f>'Cash Flow Statement'!I26</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Consolidated Gross Debt</t>
+          <t>Cash &amp; Liquid Reserves</t>
         </is>
       </c>
       <c r="C18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!C24</f>
+        <f>'Balance Sheet'!C8</f>
         <v/>
       </c>
       <c r="D18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!D24</f>
+        <f>'Balance Sheet'!D8</f>
         <v/>
       </c>
       <c r="E18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!E24</f>
+        <f>'Balance Sheet'!E8</f>
         <v/>
       </c>
       <c r="F18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!F24</f>
+        <f>'Balance Sheet'!F8</f>
         <v/>
       </c>
       <c r="G18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!G24</f>
+        <f>'Balance Sheet'!G8</f>
         <v/>
       </c>
       <c r="H18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!H24</f>
+        <f>'Balance Sheet'!H8</f>
         <v/>
       </c>
       <c r="I18" s="8">
-        <f>'Debt Schedule &amp; Tranches'!I24</f>
+        <f>'Balance Sheet'!I8</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>Consolidated Gross Debt</t>
+        </is>
+      </c>
+      <c r="C19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!C24</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!D24</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!E24</f>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!F24</f>
+        <v/>
+      </c>
+      <c r="G19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!G24</f>
+        <v/>
+      </c>
+      <c r="H19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!H24</f>
+        <v/>
+      </c>
+      <c r="I19" s="8">
+        <f>'Debt Schedule &amp; Tranches'!I24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>Consolidated Net Debt</t>
         </is>
       </c>
-      <c r="C19" s="8">
+      <c r="C20" s="8">
         <f>'Debt Schedule &amp; Tranches'!C26</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D20" s="8">
         <f>'Debt Schedule &amp; Tranches'!D26</f>
         <v/>
       </c>
-      <c r="E19" s="8">
+      <c r="E20" s="8">
         <f>'Debt Schedule &amp; Tranches'!E26</f>
         <v/>
       </c>
-      <c r="F19" s="8">
+      <c r="F20" s="8">
         <f>'Debt Schedule &amp; Tranches'!F26</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="G20" s="8">
         <f>'Debt Schedule &amp; Tranches'!G26</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H20" s="8">
         <f>'Debt Schedule &amp; Tranches'!H26</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I20" s="8">
         <f>'Debt Schedule &amp; Tranches'!I26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Net Leverage (Net Debt / EBITDA)</t>
-        </is>
-      </c>
-      <c r="C20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!C8</f>
-        <v/>
-      </c>
-      <c r="D20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!D8</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!E8</f>
-        <v/>
-      </c>
-      <c r="F20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!F8</f>
-        <v/>
-      </c>
-      <c r="G20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!G8</f>
-        <v/>
-      </c>
-      <c r="H20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!H8</f>
-        <v/>
-      </c>
-      <c r="I20" s="11">
-        <f>'Credit Metrics &amp; Ratios'!I8</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
         <is>
+          <t>Net Leverage (Calculated Cash EBITDA)</t>
+        </is>
+      </c>
+      <c r="C21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!C8</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!D8</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!E8</f>
+        <v/>
+      </c>
+      <c r="F21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!F8</f>
+        <v/>
+      </c>
+      <c r="G21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!G8</f>
+        <v/>
+      </c>
+      <c r="H21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!H8</f>
+        <v/>
+      </c>
+      <c r="I21" s="11">
+        <f>'Credit Metrics &amp; Ratios'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Net Leverage (Reported Headline EBITDA)</t>
+        </is>
+      </c>
+      <c r="C22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!C9</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!D9</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!E9</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!F9</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!G9</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!H9</f>
+        <v/>
+      </c>
+      <c r="I22" s="11">
+        <f>'Credit Metrics &amp; Ratios'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
           <t>EBITDA Interest Coverage</t>
         </is>
       </c>
-      <c r="C21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!C10</f>
-        <v/>
-      </c>
-      <c r="D21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!D10</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!E10</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!F10</f>
-        <v/>
-      </c>
-      <c r="G21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!G10</f>
-        <v/>
-      </c>
-      <c r="H21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!H10</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>'Credit Metrics &amp; Ratios'!I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="C23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!C11</f>
+        <v/>
+      </c>
+      <c r="D23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!D11</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!E11</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!F11</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!G11</f>
+        <v/>
+      </c>
+      <c r="H23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!H11</f>
+        <v/>
+      </c>
+      <c r="I23" s="12">
+        <f>'Credit Metrics &amp; Ratios'!I11</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -2089,18 +2247,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -3018,9 +3176,291 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>VI. EBITDA RECONCILIATION &amp; AUDIT BRIDGE (REPORTED VS. CALCULATED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Standardized Calculated Cash EBITDA</t>
+        </is>
+      </c>
+      <c r="C34" s="8">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="D34" s="8">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="E34" s="8">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F34" s="8">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="G34" s="8">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="H34" s="8">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="I34" s="8">
+        <f>I22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Management One-Off Adjustments &amp; Add-backs</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D35" s="24" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>COMPANY REPORTED HEADLINE EBITDA</t>
+        </is>
+      </c>
+      <c r="C36" s="20">
+        <f>C34 + C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="20">
+        <f>D34 + D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="20">
+        <f>E34 + E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="20">
+        <f>F34 + F35</f>
+        <v/>
+      </c>
+      <c r="G36" s="20">
+        <f>G34 + G35</f>
+        <v/>
+      </c>
+      <c r="H36" s="20">
+        <f>H34 + H35</f>
+        <v/>
+      </c>
+      <c r="I36" s="20">
+        <f>I34 + I35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Reconciliation Variance ($M)</t>
+        </is>
+      </c>
+      <c r="C37" s="21">
+        <f>C36 - C34</f>
+        <v/>
+      </c>
+      <c r="D37" s="21">
+        <f>D36 - D34</f>
+        <v/>
+      </c>
+      <c r="E37" s="21">
+        <f>E36 - E34</f>
+        <v/>
+      </c>
+      <c r="F37" s="21">
+        <f>F36 - F34</f>
+        <v/>
+      </c>
+      <c r="G37" s="21">
+        <f>G36 - G34</f>
+        <v/>
+      </c>
+      <c r="H37" s="21">
+        <f>H36 - H34</f>
+        <v/>
+      </c>
+      <c r="I37" s="21">
+        <f>I36 - I34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Reconciliation Variance (%)</t>
+        </is>
+      </c>
+      <c r="C38" s="22">
+        <f>C37 / C34</f>
+        <v/>
+      </c>
+      <c r="D38" s="22">
+        <f>D37 / D34</f>
+        <v/>
+      </c>
+      <c r="E38" s="22">
+        <f>E37 / E34</f>
+        <v/>
+      </c>
+      <c r="F38" s="22">
+        <f>F37 / F34</f>
+        <v/>
+      </c>
+      <c r="G38" s="22">
+        <f>G37 / G34</f>
+        <v/>
+      </c>
+      <c r="H38" s="22">
+        <f>H37 / H34</f>
+        <v/>
+      </c>
+      <c r="I38" s="22">
+        <f>I37 / I34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Reconciliation Status &amp; Audit Footnote</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+      <c r="I39" s="25" t="inlineStr">
+        <is>
+          <t>Material Add-backs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>VII. DETAILED EBITDA RECONCILIATION FOOTNOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>[2021A] Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>[2022A] Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>[2023A] Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>[2024A] Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>[2025E] Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>[2026E] Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>[2027E] Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="8">
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B47:I47"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B43:I43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4015,31 +4455,31 @@
           <t>BALANCE SHEET INTEGRITY CHECK (ASSETS - LIAB - EQUITY)</t>
         </is>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="27">
         <f>C21 - C39</f>
         <v/>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="27">
         <f>D21 - D39</f>
         <v/>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="27">
         <f>E21 - E39</f>
         <v/>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="27">
         <f>F21 - F39</f>
         <v/>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="27">
         <f>G21 - G39</f>
         <v/>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="27">
         <f>H21 - H39</f>
         <v/>
       </c>
-      <c r="I41" s="24">
+      <c r="I41" s="27">
         <f>I21 - I39</f>
         <v/>
       </c>
@@ -5497,32 +5937,32 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="G31" s="25" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>2030+</t>
         </is>
@@ -5615,7 +6055,7 @@
           <t>Senior Unsecured RegS/144A Eurobond</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -5623,15 +6063,15 @@
       <c r="E37" s="21" t="n">
         <v>300</v>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>9.000%</t>
         </is>
       </c>
-      <c r="G37" s="28" t="n">
+      <c r="G37" s="31" t="n">
         <v>94.5</v>
       </c>
-      <c r="H37" s="29" t="n">
+      <c r="H37" s="32" t="n">
         <v>11.2</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -5656,7 +6096,7 @@
           <t>Senior Secured Amortizing Project Finance Loans (EBRD / IFC / Commercial)</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -5664,15 +6104,15 @@
       <c r="E38" s="21" t="n">
         <v>720</v>
       </c>
-      <c r="F38" s="27" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>SOFR + 325 bps</t>
         </is>
       </c>
-      <c r="G38" s="28" t="n">
+      <c r="G38" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="H38" s="29" t="n">
+      <c r="H38" s="32" t="n">
         <v>8.15</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -5697,7 +6137,7 @@
           <t>Senior Secured Capex Facilities &amp; TLREF Bonds</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>TRY / EUR</t>
         </is>
@@ -5705,15 +6145,15 @@
       <c r="E39" s="21" t="n">
         <v>480</v>
       </c>
-      <c r="F39" s="27" t="inlineStr">
+      <c r="F39" s="30" t="inlineStr">
         <is>
           <t>TLREF + 350 bps / Euribor + 275 bps</t>
         </is>
       </c>
-      <c r="G39" s="28" t="n">
+      <c r="G39" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="H39" s="29" t="n">
+      <c r="H39" s="32" t="n">
         <v>14.5</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -5738,7 +6178,7 @@
           <t>Revolving Working Capital Credit Facilities</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>USD / EUR / TRY</t>
         </is>
@@ -5746,15 +6186,15 @@
       <c r="E40" s="21" t="n">
         <v>282.4</v>
       </c>
-      <c r="F40" s="27" t="inlineStr">
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>SOFR + 285 bps</t>
         </is>
       </c>
-      <c r="G40" s="28" t="n">
+      <c r="G40" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="H40" s="29" t="n">
+      <c r="H40" s="32" t="n">
         <v>7.75</v>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -5919,17 +6359,17 @@
           <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>4.50x</t>
         </is>
       </c>
-      <c r="D55" s="30" t="inlineStr">
+      <c r="D55" s="25" t="inlineStr">
         <is>
           <t>4.82x</t>
         </is>
       </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="E55" s="33" t="inlineStr">
         <is>
           <t>-0.32x leverage buffer ($-102.4M EBITDA headroom)</t>
         </is>
@@ -5946,17 +6386,17 @@
           <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>2.50x</t>
         </is>
       </c>
-      <c r="D56" s="30" t="inlineStr">
+      <c r="D56" s="25" t="inlineStr">
         <is>
           <t>2.12x</t>
         </is>
       </c>
-      <c r="E56" s="31" t="inlineStr">
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>+-0.38x interest coverage cushion</t>
         </is>
@@ -5973,17 +6413,17 @@
           <t>Maximum Permitted Priority / Secured Debt</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
         <is>
           <t>15.0% of Consolidated Total Tangible Assets</t>
         </is>
       </c>
-      <c r="D57" s="30" t="inlineStr">
+      <c r="D57" s="25" t="inlineStr">
         <is>
           <t>12.4% of Assets</t>
         </is>
       </c>
-      <c r="E57" s="31" t="inlineStr">
+      <c r="E57" s="33" t="inlineStr">
         <is>
           <t>$264.0M unutilized secured debt capacity</t>
         </is>
@@ -6000,17 +6440,17 @@
           <t>Change of Control Put Option</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
         <is>
           <t>101.00% Redemption</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
+      <c r="D58" s="25" t="inlineStr">
         <is>
           <t>N/A (Inactive)</t>
         </is>
       </c>
-      <c r="E58" s="31" t="inlineStr">
+      <c r="E58" s="33" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
@@ -6027,17 +6467,17 @@
           <t>Restricted Payments / Dividend Basket</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
         <is>
           <t>Builder Basket</t>
         </is>
       </c>
-      <c r="D59" s="30" t="inlineStr">
+      <c r="D59" s="25" t="inlineStr">
         <is>
           <t>Within Capacity</t>
         </is>
       </c>
-      <c r="E59" s="31" t="inlineStr">
+      <c r="E59" s="33" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
@@ -6054,17 +6494,17 @@
           <t>Cross-Default &amp; Cross-Acceleration</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
         <is>
           <t>$50.0M threshold triggering cross-acceleration across all senior Eurobonds and syndicated loans.</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D60" s="25" t="inlineStr">
         <is>
           <t>Zero Defaults</t>
         </is>
       </c>
-      <c r="E60" s="31" t="inlineStr">
+      <c r="E60" s="33" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
@@ -6104,7 +6544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6183,7 +6623,7 @@
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Gross Leverage (Gross Debt / EBITDA)</t>
+          <t>Gross Leverage (Gross Debt / Calculated EBITDA)</t>
         </is>
       </c>
       <c r="C7" s="12">
@@ -6218,357 +6658,427 @@
     <row r="8">
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>NET LEVERAGE (Net Debt / EBITDA)</t>
-        </is>
-      </c>
-      <c r="C8" s="32">
+          <t>NET LEVERAGE (Net Debt / Calculated Cash EBITDA)</t>
+        </is>
+      </c>
+      <c r="C8" s="34">
         <f>'Debt Schedule &amp; Tranches'!C26 / 'Income Statement (P&amp;L)'!C22</f>
         <v/>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="34">
         <f>'Debt Schedule &amp; Tranches'!D26 / 'Income Statement (P&amp;L)'!D22</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="34">
         <f>'Debt Schedule &amp; Tranches'!E26 / 'Income Statement (P&amp;L)'!E22</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="34">
         <f>'Debt Schedule &amp; Tranches'!F26 / 'Income Statement (P&amp;L)'!F22</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="34">
         <f>'Debt Schedule &amp; Tranches'!G26 / 'Income Statement (P&amp;L)'!G22</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="34">
         <f>'Debt Schedule &amp; Tranches'!H26 / 'Income Statement (P&amp;L)'!H22</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="34">
         <f>'Debt Schedule &amp; Tranches'!I26 / 'Income Statement (P&amp;L)'!I22</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>REPORTED NET LEVERAGE (Net Debt / Reported EBITDA)</t>
+        </is>
+      </c>
+      <c r="C9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!C26 / 'Income Statement (P&amp;L)'!C36</f>
+        <v/>
+      </c>
+      <c r="D9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!D26 / 'Income Statement (P&amp;L)'!D36</f>
+        <v/>
+      </c>
+      <c r="E9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!E26 / 'Income Statement (P&amp;L)'!E36</f>
+        <v/>
+      </c>
+      <c r="F9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!F26 / 'Income Statement (P&amp;L)'!F36</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!G26 / 'Income Statement (P&amp;L)'!G36</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!H26 / 'Income Statement (P&amp;L)'!H36</f>
+        <v/>
+      </c>
+      <c r="I9" s="34">
+        <f>'Debt Schedule &amp; Tranches'!I26 / 'Income Statement (P&amp;L)'!I36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Net Debt / Total Capitalization (%)</t>
         </is>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <f>'Debt Schedule &amp; Tranches'!C26 / ('Debt Schedule &amp; Tranches'!C26 + 'Balance Sheet'!C38)</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D10" s="10">
         <f>'Debt Schedule &amp; Tranches'!D26 / ('Debt Schedule &amp; Tranches'!D26 + 'Balance Sheet'!D38)</f>
         <v/>
       </c>
-      <c r="E9" s="10">
+      <c r="E10" s="10">
         <f>'Debt Schedule &amp; Tranches'!E26 / ('Debt Schedule &amp; Tranches'!E26 + 'Balance Sheet'!E38)</f>
         <v/>
       </c>
-      <c r="F9" s="10">
+      <c r="F10" s="10">
         <f>'Debt Schedule &amp; Tranches'!F26 / ('Debt Schedule &amp; Tranches'!F26 + 'Balance Sheet'!F38)</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G10" s="10">
         <f>'Debt Schedule &amp; Tranches'!G26 / ('Debt Schedule &amp; Tranches'!G26 + 'Balance Sheet'!G38)</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H10" s="10">
         <f>'Debt Schedule &amp; Tranches'!H26 / ('Debt Schedule &amp; Tranches'!H26 + 'Balance Sheet'!H38)</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I10" s="10">
         <f>'Debt Schedule &amp; Tranches'!I26 / ('Debt Schedule &amp; Tranches'!I26 + 'Balance Sheet'!I38)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>EBITDA INTEREST COVERAGE</t>
-        </is>
-      </c>
-      <c r="C10" s="32">
+    <row r="11">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>EBITDA INTEREST COVERAGE (Calculated Cash EBITDA)</t>
+        </is>
+      </c>
+      <c r="C11" s="34">
         <f>'Income Statement (P&amp;L)'!C22 / 'Debt Schedule &amp; Tranches'!C28</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D11" s="34">
         <f>'Income Statement (P&amp;L)'!D22 / 'Debt Schedule &amp; Tranches'!D28</f>
         <v/>
       </c>
-      <c r="E10" s="32">
+      <c r="E11" s="34">
         <f>'Income Statement (P&amp;L)'!E22 / 'Debt Schedule &amp; Tranches'!E28</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F11" s="34">
         <f>'Income Statement (P&amp;L)'!F22 / 'Debt Schedule &amp; Tranches'!F28</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G11" s="34">
         <f>'Income Statement (P&amp;L)'!G22 / 'Debt Schedule &amp; Tranches'!G28</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H11" s="34">
         <f>'Income Statement (P&amp;L)'!H22 / 'Debt Schedule &amp; Tranches'!H28</f>
         <v/>
       </c>
-      <c r="I10" s="32">
+      <c r="I11" s="34">
         <f>'Income Statement (P&amp;L)'!I22 / 'Debt Schedule &amp; Tranches'!I28</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Reported EBITDA Interest Coverage (Reported EBITDA)</t>
+        </is>
+      </c>
+      <c r="C12" s="12">
+        <f>'Income Statement (P&amp;L)'!C36 / 'Debt Schedule &amp; Tranches'!C28</f>
+        <v/>
+      </c>
+      <c r="D12" s="12">
+        <f>'Income Statement (P&amp;L)'!D36 / 'Debt Schedule &amp; Tranches'!D28</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
+        <f>'Income Statement (P&amp;L)'!E36 / 'Debt Schedule &amp; Tranches'!E28</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>'Income Statement (P&amp;L)'!F36 / 'Debt Schedule &amp; Tranches'!F28</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>'Income Statement (P&amp;L)'!G36 / 'Debt Schedule &amp; Tranches'!G28</f>
+        <v/>
+      </c>
+      <c r="H12" s="12">
+        <f>'Income Statement (P&amp;L)'!H36 / 'Debt Schedule &amp; Tranches'!H28</f>
+        <v/>
+      </c>
+      <c r="I12" s="12">
+        <f>'Income Statement (P&amp;L)'!I36 / 'Debt Schedule &amp; Tranches'!I28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>EBIT Interest Coverage</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C13" s="12">
         <f>'Income Statement (P&amp;L)'!C25 / 'Debt Schedule &amp; Tranches'!C28</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D13" s="12">
         <f>'Income Statement (P&amp;L)'!D25 / 'Debt Schedule &amp; Tranches'!D28</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E13" s="12">
         <f>'Income Statement (P&amp;L)'!E25 / 'Debt Schedule &amp; Tranches'!E28</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F13" s="12">
         <f>'Income Statement (P&amp;L)'!F25 / 'Debt Schedule &amp; Tranches'!F28</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G13" s="12">
         <f>'Income Statement (P&amp;L)'!G25 / 'Debt Schedule &amp; Tranches'!G28</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H13" s="12">
         <f>'Income Statement (P&amp;L)'!H25 / 'Debt Schedule &amp; Tranches'!H28</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I13" s="12">
         <f>'Income Statement (P&amp;L)'!I25 / 'Debt Schedule &amp; Tranches'!I28</f>
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>II. CASH FLOW COVERAGE &amp; LIQUIDITY RATIOS</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>CFO / Gross Debt (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="10">
-        <f>'Cash Flow Statement'!C14 / 'Debt Schedule &amp; Tranches'!C24</f>
-        <v/>
-      </c>
-      <c r="D14" s="10">
-        <f>'Cash Flow Statement'!D14 / 'Debt Schedule &amp; Tranches'!D24</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>'Cash Flow Statement'!E14 / 'Debt Schedule &amp; Tranches'!E24</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>'Cash Flow Statement'!F14 / 'Debt Schedule &amp; Tranches'!F24</f>
-        <v/>
-      </c>
-      <c r="G14" s="10">
-        <f>'Cash Flow Statement'!G14 / 'Debt Schedule &amp; Tranches'!G24</f>
-        <v/>
-      </c>
-      <c r="H14" s="10">
-        <f>'Cash Flow Statement'!H14 / 'Debt Schedule &amp; Tranches'!H24</f>
-        <v/>
-      </c>
-      <c r="I14" s="10">
-        <f>'Cash Flow Statement'!I14 / 'Debt Schedule &amp; Tranches'!I24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>FCF / Net Debt (%)</t>
-        </is>
-      </c>
-      <c r="C15" s="10">
-        <f>'Cash Flow Statement'!C28 / 'Debt Schedule &amp; Tranches'!C26</f>
-        <v/>
-      </c>
-      <c r="D15" s="10">
-        <f>'Cash Flow Statement'!D28 / 'Debt Schedule &amp; Tranches'!D26</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>'Cash Flow Statement'!E28 / 'Debt Schedule &amp; Tranches'!E26</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>'Cash Flow Statement'!F28 / 'Debt Schedule &amp; Tranches'!F26</f>
-        <v/>
-      </c>
-      <c r="G15" s="10">
-        <f>'Cash Flow Statement'!G28 / 'Debt Schedule &amp; Tranches'!G26</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
-        <f>'Cash Flow Statement'!H28 / 'Debt Schedule &amp; Tranches'!H26</f>
-        <v/>
-      </c>
-      <c r="I15" s="10">
-        <f>'Cash Flow Statement'!I28 / 'Debt Schedule &amp; Tranches'!I26</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>FCF Conversion Ratio (FCF / EBITDA)</t>
+          <t>CFO / Gross Debt (%)</t>
         </is>
       </c>
       <c r="C16" s="10">
-        <f>'Cash Flow Statement'!C28 / 'Income Statement (P&amp;L)'!C22</f>
+        <f>'Cash Flow Statement'!C14 / 'Debt Schedule &amp; Tranches'!C24</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>'Cash Flow Statement'!D28 / 'Income Statement (P&amp;L)'!D22</f>
+        <f>'Cash Flow Statement'!D14 / 'Debt Schedule &amp; Tranches'!D24</f>
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>'Cash Flow Statement'!E28 / 'Income Statement (P&amp;L)'!E22</f>
+        <f>'Cash Flow Statement'!E14 / 'Debt Schedule &amp; Tranches'!E24</f>
         <v/>
       </c>
       <c r="F16" s="10">
-        <f>'Cash Flow Statement'!F28 / 'Income Statement (P&amp;L)'!F22</f>
+        <f>'Cash Flow Statement'!F14 / 'Debt Schedule &amp; Tranches'!F24</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>'Cash Flow Statement'!G28 / 'Income Statement (P&amp;L)'!G22</f>
+        <f>'Cash Flow Statement'!G14 / 'Debt Schedule &amp; Tranches'!G24</f>
         <v/>
       </c>
       <c r="H16" s="10">
-        <f>'Cash Flow Statement'!H28 / 'Income Statement (P&amp;L)'!H22</f>
+        <f>'Cash Flow Statement'!H14 / 'Debt Schedule &amp; Tranches'!H24</f>
         <v/>
       </c>
       <c r="I16" s="10">
-        <f>'Cash Flow Statement'!I28 / 'Income Statement (P&amp;L)'!I22</f>
+        <f>'Cash Flow Statement'!I14 / 'Debt Schedule &amp; Tranches'!I24</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Capex / Operating Cash Flow (%)</t>
+          <t>FCF / Net Debt (%)</t>
         </is>
       </c>
       <c r="C17" s="10">
-        <f>-'Cash Flow Statement'!C16 / 'Cash Flow Statement'!C14</f>
+        <f>'Cash Flow Statement'!C28 / 'Debt Schedule &amp; Tranches'!C26</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>-'Cash Flow Statement'!D16 / 'Cash Flow Statement'!D14</f>
+        <f>'Cash Flow Statement'!D28 / 'Debt Schedule &amp; Tranches'!D26</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>-'Cash Flow Statement'!E16 / 'Cash Flow Statement'!E14</f>
+        <f>'Cash Flow Statement'!E28 / 'Debt Schedule &amp; Tranches'!E26</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>-'Cash Flow Statement'!F16 / 'Cash Flow Statement'!F14</f>
+        <f>'Cash Flow Statement'!F28 / 'Debt Schedule &amp; Tranches'!F26</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>-'Cash Flow Statement'!G16 / 'Cash Flow Statement'!G14</f>
+        <f>'Cash Flow Statement'!G28 / 'Debt Schedule &amp; Tranches'!G26</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>-'Cash Flow Statement'!H16 / 'Cash Flow Statement'!H14</f>
+        <f>'Cash Flow Statement'!H28 / 'Debt Schedule &amp; Tranches'!H26</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>-'Cash Flow Statement'!I16 / 'Cash Flow Statement'!I14</f>
+        <f>'Cash Flow Statement'!I28 / 'Debt Schedule &amp; Tranches'!I26</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Current Ratio (Current Assets / Current Liab)</t>
-        </is>
-      </c>
-      <c r="C18" s="12">
-        <f>'Balance Sheet'!C11 / 'Balance Sheet'!C27</f>
-        <v/>
-      </c>
-      <c r="D18" s="12">
-        <f>'Balance Sheet'!D11 / 'Balance Sheet'!D27</f>
-        <v/>
-      </c>
-      <c r="E18" s="12">
-        <f>'Balance Sheet'!E11 / 'Balance Sheet'!E27</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
-        <f>'Balance Sheet'!F11 / 'Balance Sheet'!F27</f>
-        <v/>
-      </c>
-      <c r="G18" s="12">
-        <f>'Balance Sheet'!G11 / 'Balance Sheet'!G27</f>
-        <v/>
-      </c>
-      <c r="H18" s="12">
-        <f>'Balance Sheet'!H11 / 'Balance Sheet'!H27</f>
-        <v/>
-      </c>
-      <c r="I18" s="12">
-        <f>'Balance Sheet'!I11 / 'Balance Sheet'!I27</f>
+          <t>FCF Conversion Ratio (FCF / EBITDA)</t>
+        </is>
+      </c>
+      <c r="C18" s="10">
+        <f>'Cash Flow Statement'!C28 / 'Income Statement (P&amp;L)'!C22</f>
+        <v/>
+      </c>
+      <c r="D18" s="10">
+        <f>'Cash Flow Statement'!D28 / 'Income Statement (P&amp;L)'!D22</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>'Cash Flow Statement'!E28 / 'Income Statement (P&amp;L)'!E22</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>'Cash Flow Statement'!F28 / 'Income Statement (P&amp;L)'!F22</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>'Cash Flow Statement'!G28 / 'Income Statement (P&amp;L)'!G22</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>'Cash Flow Statement'!H28 / 'Income Statement (P&amp;L)'!H22</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>'Cash Flow Statement'!I28 / 'Income Statement (P&amp;L)'!I22</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>Capex / Operating Cash Flow (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>-'Cash Flow Statement'!C16 / 'Cash Flow Statement'!C14</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>-'Cash Flow Statement'!D16 / 'Cash Flow Statement'!D14</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>-'Cash Flow Statement'!E16 / 'Cash Flow Statement'!E14</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>-'Cash Flow Statement'!F16 / 'Cash Flow Statement'!F14</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>-'Cash Flow Statement'!G16 / 'Cash Flow Statement'!G14</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>-'Cash Flow Statement'!H16 / 'Cash Flow Statement'!H14</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>-'Cash Flow Statement'!I16 / 'Cash Flow Statement'!I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Current Ratio (Current Assets / Current Liab)</t>
+        </is>
+      </c>
+      <c r="C20" s="12">
+        <f>'Balance Sheet'!C11 / 'Balance Sheet'!C27</f>
+        <v/>
+      </c>
+      <c r="D20" s="12">
+        <f>'Balance Sheet'!D11 / 'Balance Sheet'!D27</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>'Balance Sheet'!E11 / 'Balance Sheet'!E27</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>'Balance Sheet'!F11 / 'Balance Sheet'!F27</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>'Balance Sheet'!G11 / 'Balance Sheet'!G27</f>
+        <v/>
+      </c>
+      <c r="H20" s="12">
+        <f>'Balance Sheet'!H11 / 'Balance Sheet'!H27</f>
+        <v/>
+      </c>
+      <c r="I20" s="12">
+        <f>'Balance Sheet'!I11 / 'Balance Sheet'!I27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>Quick Ratio ((Cash + AR) / Current Liab)</t>
         </is>
       </c>
-      <c r="C19" s="12">
+      <c r="C21" s="12">
         <f>('Balance Sheet'!C7 + 'Balance Sheet'!C8) / 'Balance Sheet'!C27</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D21" s="12">
         <f>('Balance Sheet'!D7 + 'Balance Sheet'!D8) / 'Balance Sheet'!D27</f>
         <v/>
       </c>
-      <c r="E19" s="12">
+      <c r="E21" s="12">
         <f>('Balance Sheet'!E7 + 'Balance Sheet'!E8) / 'Balance Sheet'!E27</f>
         <v/>
       </c>
-      <c r="F19" s="12">
+      <c r="F21" s="12">
         <f>('Balance Sheet'!F7 + 'Balance Sheet'!F8) / 'Balance Sheet'!F27</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="G21" s="12">
         <f>('Balance Sheet'!G7 + 'Balance Sheet'!G8) / 'Balance Sheet'!G27</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H21" s="12">
         <f>('Balance Sheet'!H7 + 'Balance Sheet'!H8) / 'Balance Sheet'!H27</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I21" s="12">
         <f>('Balance Sheet'!I7 + 'Balance Sheet'!I8) / 'Balance Sheet'!I27</f>
         <v/>
       </c>
@@ -6622,37 +7132,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Scenario Name</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Revenue Drop</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Margin Compression</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Refinancing Rate</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Exit EV Multiple</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Implied Recovery Px</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>Upside / Downside</t>
         </is>
@@ -6664,32 +7174,32 @@
           <t>Base Case (Consensus Forecast)</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>0 bp</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>11.20%</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>4.2x</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>$95.00</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>+0.5%</t>
         </is>
@@ -6701,32 +7211,32 @@
           <t>Downside Stress Case (Recession)</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>-15.0%</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>-300 bp</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>13.20%</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>3.2x</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>$76.50</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="30" t="inlineStr">
         <is>
           <t>-19.0%</t>
         </is>
@@ -6738,32 +7248,32 @@
           <t>Severe Distressed Floor (Liquidation)</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>-35.0%</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>-650 bp</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>+500 bp spread</t>
         </is>
       </c>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Liquidation Value</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>$58.00</t>
         </is>
       </c>
-      <c r="H8" s="27" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>-38.6%</t>
         </is>
@@ -6775,32 +7285,32 @@
           <t>Bull Case (Cycle Peak / Accretion)</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>+12.0%</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>+200 bp</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>9.70%</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>5.7x</t>
         </is>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>$105.00</t>
         </is>
       </c>
-      <c r="H9" s="27" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>+11.1%</t>
         </is>
@@ -6816,32 +7326,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Tranche Claim</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Claim Amount ($M)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>Seniority Ranking</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>Estimated Collateral</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Recovery Floor (%)</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Base Recovery (%)</t>
         </is>
@@ -6866,12 +7376,12 @@
           <t>First Lien Fixed Charges</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -6896,12 +7406,12 @@
           <t>General Corporate Guarantee</t>
         </is>
       </c>
-      <c r="F15" s="27" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>58.0%</t>
         </is>
       </c>
-      <c r="G15" s="27" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>95.0%</t>
         </is>
@@ -6926,12 +7436,12 @@
           <t>Junior Unsecured Claim</t>
         </is>
       </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
@@ -6956,12 +7466,12 @@
           <t>Ordinary Shares</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>Residual Only</t>
         </is>
@@ -7077,17 +7587,17 @@
           <t>$1,280M - $1,320M (+8.0% YoY)</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>$1,295M annualized (9M24 actuals)</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>On Track</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
         <is>
           <t>High geothermal plant availability (88.5%) and steady OEDAS distribution volume (+3.8%) tracking in line with guidance envelope.</t>
         </is>
@@ -7104,17 +7614,17 @@
           <t>$330M - $350M (26.5% - 27.5% margin)</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>$338M annualized run-rate</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>On Track</t>
         </is>
       </c>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>USD-denominated YEKDEM cash flows ($105-$132/MWh) generated 68.5% of generation EBITDA, protecting margins against TRY depreciation.</t>
         </is>
@@ -7131,17 +7641,17 @@
           <t>&lt; 3.50x Net Debt / EBITDA</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>4.82x Net Debt / EBITDA (2024A)</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Under Watch</t>
         </is>
       </c>
-      <c r="F9" s="36" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>Elevated leverage due to TRY translation of unhedged debt; deleveraging milestone contingent on executing Zorlu Yenilenebilir equity monetization.</t>
         </is>
@@ -7158,17 +7668,17 @@
           <t>&lt; $115.0M maximum capex envelope</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>$108.2M committed / incurred</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>On Track</t>
         </is>
       </c>
-      <c r="F10" s="36" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>Discretionary thermal capex frozen; capital deployed exclusively into regulated OEDAS grid capex (RAB-accretive) and Kizildere hybrid solar.</t>
         </is>
@@ -7185,17 +7695,17 @@
           <t>2,200+ public sockets by end-2025</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>1,850 sockets active across 81 provinces</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>Ahead of Target</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="38" t="inlineStr">
         <is>
           <t>Consolidated #1 market position in Turkey with 38% market share; Electrip international pilot expanding across Italy, France, and Poland.</t>
         </is>
@@ -7227,7 +7737,7 @@
           <t>Kizildere Hybrid Solar</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>50 MW co-located solar PV under construction at Kizildere to utilize existing transmission capacity and boost summer generation</t>
         </is>
@@ -7239,7 +7749,7 @@
           <t>Alasehir Geothermal Expansion</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Preliminary drilling and resource appraisal for Alasehir II geothermal project (potential +30 MW expansion)</t>
         </is>
@@ -7251,7 +7761,7 @@
           <t>Oedas Smart Grid Investments</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TRY 3.8B committed grid modernization and digital substation automation under 4th Tariff Period</t>
         </is>
@@ -7263,7 +7773,7 @@
           <t>Zes Electrip Europe</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Targeting 500 ultra-fast DC charging hubs across Southern and Central Europe by 2026</t>
         </is>
@@ -7295,7 +7805,7 @@
           <t>Usd Revenue Share</t>
         </is>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>68.5% of generation EBITDA earned in US Dollars directly under statutory YEKDEM mechanism</t>
         </is>
@@ -7307,7 +7817,7 @@
           <t>Try Regulated Revenue Share</t>
         </is>
       </c>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>31.5% of revenue earned in Turkish Lira via OEDAS/OEPSAS with full CPI inflation pass-through</t>
         </is>
@@ -7319,7 +7829,7 @@
           <t>Debt Currency Denomination</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>58% USD, 24% EUR, 18% TRY — natural dollar hedge covers 100% of USD net interest payments</t>
         </is>
@@ -7331,7 +7841,7 @@
           <t>Fx Risk Mitigation</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>Bilateral FX forward hedges covering next 12-month EUR debt principal amortizations</t>
         </is>
@@ -7363,7 +7873,7 @@
           <t>Contracted Generation Capacity</t>
         </is>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>643 MW operating under government-backed take-or-pay feed-in tariffs</t>
         </is>
@@ -7375,7 +7885,7 @@
           <t>Offtaker Counterparty</t>
         </is>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>Republic of Turkey Ministry of Energy and Natural Resources / EPIAS (100% sovereign-backed offtake)</t>
         </is>
@@ -7387,7 +7897,7 @@
           <t>Average Concession Life</t>
         </is>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>Distribution concession through 2036; Geothermal exploration licenses valid through 2041-2047</t>
         </is>
@@ -7419,7 +7929,7 @@
           <t>Unrestricted Cash Reserves</t>
         </is>
       </c>
-      <c r="C35" s="36" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>$240.0M held in tier-1 commercial and state banks (Akbank, Garanti, Isbank)</t>
         </is>
@@ -7431,7 +7941,7 @@
           <t>Undrawn Committed Facilities</t>
         </is>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>$180.0M undrawn revolving credit lines and overdraft limits</t>
         </is>
@@ -7443,7 +7953,7 @@
           <t>Next 12M Debt Service</t>
         </is>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>$260.0M scheduled amortization and coupon payments fully covered by internal operating cash flow ($272M CFO)</t>
         </is>
@@ -7474,7 +7984,7 @@
           <t>Geothermal Capacity Jes</t>
         </is>
       </c>
-      <c r="C40" s="36" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>305.0 MW total geothermal capacity: Kizildere I (15.0 MW), Kizildere II (80.0 MW), Kizildere III Unit 1 (99.5 MW), Kizildere III Unit 2 (65.5 MW), Alasehir I (45.0 MW) — Turkey's largest and lowest-cost baseload renewable fleet</t>
         </is>
@@ -7486,7 +7996,7 @@
           <t>Wind Capacity Res</t>
         </is>
       </c>
-      <c r="C41" s="36" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>135.0 MW Gokcedag Wind Power Plant (Osmaniye) — long-term high wind resource capacity factor (&gt;34%)</t>
         </is>
@@ -7498,7 +8008,7 @@
           <t>Hydroelectric Capacity Hes</t>
         </is>
       </c>
-      <c r="C42" s="36" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>118.6 MW across 7 operating run-of-river and reservoir plants (Ikizdere, Atabey, Camlica, Kuzgun, Mercan, Tercan, Beykoy)</t>
         </is>
@@ -7510,7 +8020,7 @@
           <t>Solar And Hybrid Capacity</t>
         </is>
       </c>
-      <c r="C43" s="36" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>84.0 MW installed and under development (hybrid solar installations co-located at Kizildere geothermal sites)</t>
         </is>
@@ -7522,7 +8032,7 @@
           <t>Thermal And Industrial Cogen</t>
         </is>
       </c>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>341.0 MW domestic gas cogeneration and district heating (Bursa, Luleburgaz)</t>
         </is>
@@ -7534,7 +8044,7 @@
           <t>International Power Assets</t>
         </is>
       </c>
-      <c r="C45" s="36" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>290.4 MW total international holdings: 56.4 MW Jhimpir Wind (Pakistan, sovereign USD PPA) + 25.0% equity interest in 840 MW Dorad Energy (Israel, 210 MW net share)</t>
         </is>
@@ -7566,7 +8076,7 @@
           <t>Geothermal Dollar Tariff</t>
         </is>
       </c>
-      <c r="C49" s="36" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>$105.0/MWh base feed-in tariff + up to $27.0/MWh domestic equipment component bonus = $132.0/MWh guaranteed in US Dollars</t>
         </is>
@@ -7578,7 +8088,7 @@
           <t>Wind Dollar Tariff</t>
         </is>
       </c>
-      <c r="C50" s="36" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>$73.0/MWh base tariff + up to $21.0/MWh local blade/tower manufacturing bonus = $94.0/MWh guaranteed in US Dollars</t>
         </is>
@@ -7590,7 +8100,7 @@
           <t>Dollar Natural Hedge Ratio</t>
         </is>
       </c>
-      <c r="C51" s="36" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>68.5% of total power generation cash EBITDA is received in hard currency US Dollars via YEKDEM settlement, fully covering annual USD debt service on project loans and Eurobonds</t>
         </is>
@@ -7602,7 +8112,7 @@
           <t>Yekdem Contract Expiry Schedule</t>
         </is>
       </c>
-      <c r="C52" s="36" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>Kizildere II active through 2026; Alasehir active through 2026; Kizildere III Unit 1 through 2028; Kizildere III Unit 2 through 2029; Gokcedag Wind through 2025 (transitioning to merchant/bilateral contracts)</t>
         </is>
@@ -7634,7 +8144,7 @@
           <t>Concession Area</t>
         </is>
       </c>
-      <c r="C56" s="36" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>Osmangazi electricity distribution region covering 5 provinces: Afyonkarahisar, Bilecik, Eskisehir, Kutahya, Usak</t>
         </is>
@@ -7646,7 +8156,7 @@
           <t>Customer Reach</t>
         </is>
       </c>
-      <c r="C57" s="36" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>1.95 million registered meters serving a regional population of ~2.9 million</t>
         </is>
@@ -7658,7 +8168,7 @@
           <t>Annual Volume Distributed</t>
         </is>
       </c>
-      <c r="C58" s="36" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>8,650 GWh distributed electricity volume (+3.8% organic growth in 2024)</t>
         </is>
@@ -7670,7 +8180,7 @@
           <t>Regulated Asset Base Rab</t>
         </is>
       </c>
-      <c r="C59" s="36" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>$650.0M equivalent (TRY 22.5B), earning a real pre-tax allowed return on equity (WACC) set by EMRA (12.3% real return)</t>
         </is>
@@ -7682,7 +8192,7 @@
           <t>Inflation Protection</t>
         </is>
       </c>
-      <c r="C60" s="36" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>Distribution tariffs and opex/capex allowances are adjusted monthly for Turkish CPI/PPI, shielding real operating margin against currency depreciation</t>
         </is>
@@ -7713,7 +8223,7 @@
           <t>Active Charging Sockets</t>
         </is>
       </c>
-      <c r="C64" s="36" t="inlineStr">
+      <c r="C64" s="38" t="inlineStr">
         <is>
           <t>1,850+ public AC/DC fast-charging sockets operating across all 81 provinces of Turkey</t>
         </is>
@@ -7725,7 +8235,7 @@
           <t>Market Share</t>
         </is>
       </c>
-      <c r="C65" s="36" t="inlineStr">
+      <c r="C65" s="38" t="inlineStr">
         <is>
           <t>~35% - 38% market share in public DC fast charging, maintaining clear #1 market leadership in Turkey</t>
         </is>
@@ -7737,7 +8247,7 @@
           <t>European Expansion Electrip</t>
         </is>
       </c>
-      <c r="C66" s="36" t="inlineStr">
+      <c r="C66" s="38" t="inlineStr">
         <is>
           <t>International EV charging rollout under the Electrip brand with active high-power hubs launched in Italy, France, Poland, Bulgaria, and Greece</t>
         </is>
@@ -7749,7 +8259,7 @@
           <t>Charging Volume Growth</t>
         </is>
       </c>
-      <c r="C67" s="36" t="inlineStr">
+      <c r="C67" s="38" t="inlineStr">
         <is>
           <t>+78.0% YoY increase in electricity delivered via charging network (transitioning into high-margin recurring cash flow stream)</t>
         </is>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -481,6 +481,65 @@
     <author>CEMBI Credit Desk</author>
   </authors>
   <commentList>
+    <comment ref="C34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2021A):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+FCF of $114M generated, funding interest payments and early turbine maintenance.</t>
+      </text>
+    </comment>
+    <comment ref="D34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2022A):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+Strong operating cash flow ($225M) enabled $128M in free cash flow after all capex commitments.</t>
+      </text>
+    </comment>
+    <comment ref="E34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2023A):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+FCF generation reached $142M, allowing scheduled project finance amortization payments.</t>
+      </text>
+    </comment>
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2024A):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+Strong FCF of $160M generated, maintaining unrestricted cash reserves at $240M across partner banks.</t>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2025E):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+Projected FCF of $181.4M provides robust liquidity runway covering 100% of upcoming debt service.</t>
+      </text>
+    </comment>
+    <comment ref="H34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2026E):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+Free cash flow expands to $207M, providing substantial balance sheet flexibility for Eurobond refinancing.</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>CEMBI Credit Desk FCF Bridge (2027E):
+Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
+FCF generation hits $229M, completely self-funding all ongoing operational and capital requirements.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CEMBI Credit Desk</author>
+  </authors>
+  <commentList>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2021A):
@@ -1173,31 +1232,31 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>'Cash Flow Statement'!C26</f>
+        <f>'Cash Flow Statement'!C34</f>
         <v/>
       </c>
       <c r="D17" s="8">
-        <f>'Cash Flow Statement'!D26</f>
+        <f>'Cash Flow Statement'!D34</f>
         <v/>
       </c>
       <c r="E17" s="8">
-        <f>'Cash Flow Statement'!E26</f>
+        <f>'Cash Flow Statement'!E34</f>
         <v/>
       </c>
       <c r="F17" s="8">
-        <f>'Cash Flow Statement'!F26</f>
+        <f>'Cash Flow Statement'!F34</f>
         <v/>
       </c>
       <c r="G17" s="8">
-        <f>'Cash Flow Statement'!G26</f>
+        <f>'Cash Flow Statement'!G34</f>
         <v/>
       </c>
       <c r="H17" s="8">
-        <f>'Cash Flow Statement'!H26</f>
+        <f>'Cash Flow Statement'!H34</f>
         <v/>
       </c>
       <c r="I17" s="8">
-        <f>'Cash Flow Statement'!I26</f>
+        <f>'Cash Flow Statement'!I34</f>
         <v/>
       </c>
     </row>
@@ -4498,7 +4557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5154,45 +5213,320 @@
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>FREE CASH FLOW (FCF = CFO + Capex)</t>
-        </is>
-      </c>
-      <c r="C28" s="16">
-        <f>C14 + C16</f>
-        <v/>
-      </c>
-      <c r="D28" s="16">
-        <f>D14 + D16</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f>E14 + E16</f>
-        <v/>
-      </c>
-      <c r="F28" s="16">
-        <f>F14 + F16</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>G14 + G16</f>
-        <v/>
-      </c>
-      <c r="H28" s="16">
-        <f>H14 + H16</f>
-        <v/>
-      </c>
-      <c r="I28" s="16">
-        <f>I14 + I16</f>
-        <v/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>IV. FREE CASH FLOW (FCF) WATERFALL BRIDGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Calculated Cash EBITDA (Operating Cash Profit)</t>
+        </is>
+      </c>
+      <c r="C29" s="20">
+        <f>'Income Statement (P&amp;L)'!C22</f>
+        <v/>
+      </c>
+      <c r="D29" s="20">
+        <f>'Income Statement (P&amp;L)'!D22</f>
+        <v/>
+      </c>
+      <c r="E29" s="20">
+        <f>'Income Statement (P&amp;L)'!E22</f>
+        <v/>
+      </c>
+      <c r="F29" s="20">
+        <f>'Income Statement (P&amp;L)'!F22</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>'Income Statement (P&amp;L)'!G22</f>
+        <v/>
+      </c>
+      <c r="H29" s="20">
+        <f>'Income Statement (P&amp;L)'!H22</f>
+        <v/>
+      </c>
+      <c r="I29" s="20">
+        <f>'Income Statement (P&amp;L)'!I22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Less: Capital Expenditures (Capex)</t>
+        </is>
+      </c>
+      <c r="C30" s="8">
+        <f>ABS(C16)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>ABS(D16)</f>
+        <v/>
+      </c>
+      <c r="E30" s="8">
+        <f>ABS(E16)</f>
+        <v/>
+      </c>
+      <c r="F30" s="8">
+        <f>ABS(F16)</f>
+        <v/>
+      </c>
+      <c r="G30" s="8">
+        <f>ABS(G16)</f>
+        <v/>
+      </c>
+      <c r="H30" s="8">
+        <f>ABS(H16)</f>
+        <v/>
+      </c>
+      <c r="I30" s="8">
+        <f>ABS(I16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Less: Net Cash Interest Paid</t>
+        </is>
+      </c>
+      <c r="C31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!C28</f>
+        <v/>
+      </c>
+      <c r="D31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!D28</f>
+        <v/>
+      </c>
+      <c r="E31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!E28</f>
+        <v/>
+      </c>
+      <c r="F31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!F28</f>
+        <v/>
+      </c>
+      <c r="G31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!G28</f>
+        <v/>
+      </c>
+      <c r="H31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!H28</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>'Debt Schedule &amp; Tranches'!I28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Less: Net Working Capital Investment (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>-59.3</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>-79.40000000000001</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-97.09999999999999</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>-113.9</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>-107.3</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>-97.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Less: Cash Income Taxes Paid</t>
+        </is>
+      </c>
+      <c r="C33" s="8">
+        <f>'Income Statement (P&amp;L)'!C30</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>'Income Statement (P&amp;L)'!D30</f>
+        <v/>
+      </c>
+      <c r="E33" s="8">
+        <f>'Income Statement (P&amp;L)'!E30</f>
+        <v/>
+      </c>
+      <c r="F33" s="8">
+        <f>'Income Statement (P&amp;L)'!F30</f>
+        <v/>
+      </c>
+      <c r="G33" s="8">
+        <f>'Income Statement (P&amp;L)'!G30</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>'Income Statement (P&amp;L)'!H30</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>'Income Statement (P&amp;L)'!I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>FREE CASH FLOW (FCF = EBITDA - Capex - Interest - ΔNWC - Tax)</t>
+        </is>
+      </c>
+      <c r="C34" s="20">
+        <f>C29 - C30 - C31 - C32 - C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f>D29 - D30 - D31 - D32 - D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="20">
+        <f>E29 - E30 - E31 - E32 - E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="20">
+        <f>F29 - F30 - F31 - F32 - F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="20">
+        <f>G29 - G30 - G31 - G32 - G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="20">
+        <f>H29 - H30 - H31 - H32 - H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="20">
+        <f>I29 - I30 - I31 - I32 - I33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>FCF Conversion Ratio (% of EBITDA)</t>
+        </is>
+      </c>
+      <c r="C35" s="22">
+        <f>C34 / C29</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f>D34 / D29</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f>E34 / E29</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f>F34 / F29</f>
+        <v/>
+      </c>
+      <c r="G35" s="22">
+        <f>G34 / G29</f>
+        <v/>
+      </c>
+      <c r="H35" s="22">
+        <f>H34 / H29</f>
+        <v/>
+      </c>
+      <c r="I35" s="22">
+        <f>I34 / I29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>V. FREE CASH FLOW COMMENTARY &amp; CAPITAL ALLOCATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>[2021A] FCF of $114M generated, funding interest payments and early turbine maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>[2022A] Strong operating cash flow ($225M) enabled $128M in free cash flow after all capex commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>[2023A] FCF generation reached $142M, allowing scheduled project finance amortization payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>[2024A] Strong FCF of $160M generated, maintaining unrestricted cash reserves at $240M across partner banks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>[2025E] Projected FCF of $181.4M provides robust liquidity runway covering 100% of upcoming debt service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>[2026E] Free cash flow expands to $207M, providing substantial balance sheet flexibility for Eurobond refinancing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>[2027E] FCF generation hits $229M, completely self-funding all ongoing operational and capital requirements.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="8">
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B38:I38"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -7843,7 +7843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8388,7 +8388,7 @@
     <row r="47">
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>VII. YEKDEM FEED IN TARIFF MECHANICS</t>
+          <t>VI. YEKDEM FEED IN TARIFF MECHANICS</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
     <row r="54">
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>VIII. DISTRIBUTION AND RETAIL OEDAS</t>
+          <t>VI. DISTRIBUTION AND RETAIL OEDAS</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
     <row r="62">
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>IX. ZES ELECTRIC VEHICLE CHARGING NETWORK</t>
+          <t>VI. ZES ELECTRIC VEHICLE CHARGING NETWORK</t>
         </is>
       </c>
     </row>
@@ -8599,8 +8599,87 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C72" s="38" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Reporting Period</t>
+        </is>
+      </c>
+      <c r="C73" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2026 / 9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Webcast Schedule</t>
+        </is>
+      </c>
+      <c r="C75" s="38" t="inlineStr">
+        <is>
+          <t>18:00 Istanbul (Post-Market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Official IR Portal / Webcast URL</t>
+        </is>
+      </c>
+      <c r="C76" s="38" t="inlineStr">
+        <is>
+          <t>https://www.zoren.com.tr/en/investor-relations/financial-reports</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="54">
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C52:I52"/>
@@ -8609,6 +8688,7 @@
     <mergeCell ref="C48:I48"/>
     <mergeCell ref="C39:I39"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C72:I72"/>
     <mergeCell ref="C67:I67"/>
     <mergeCell ref="C57:I57"/>
     <mergeCell ref="C37:I37"/>
@@ -8627,9 +8707,11 @@
     <mergeCell ref="C58:I58"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C45:I45"/>
+    <mergeCell ref="C74:I74"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="C64:I64"/>
     <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C73:I73"/>
     <mergeCell ref="C29:I29"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C25:I25"/>
@@ -8640,6 +8722,7 @@
     <mergeCell ref="C50:I50"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C44:I44"/>
+    <mergeCell ref="C75:I75"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="C40:I40"/>
     <mergeCell ref="F8:I8"/>
@@ -8649,6 +8732,8 @@
     <mergeCell ref="C43:I43"/>
     <mergeCell ref="C60:I60"/>
     <mergeCell ref="C51:I51"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -262,6 +262,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7843,7 +7846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8602,102 +8605,205 @@
     <row r="70">
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+          <t>INSTITUTIONAL MANAGEMENT QUESTIONS &amp; CONVICTION DRIVERS (1-ON-1 DUE DILIGENCE)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Calendar Dimension</t>
+          <t>Focus Area</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Detail &amp; IR Access</t>
+          <t>Question to Ask CFO / Management</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Credit Relevance &amp; Deduced Ambiguity</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Conviction Trigger &amp; Decision Rule</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Next Scheduled Earnings Date</t>
+          <t>YEKDEM Dollar Conversion &amp; Central Bank FX Surrender Lag</t>
         </is>
       </c>
       <c r="C72" s="38" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>Can you provide the exact operational mechanics and timeline for converting TRY electricity sales into hard-currency USD under the YEKDEM mechanism? Specifically, does Zorlu face any repatriation friction or mandatory central bank surrender ratios that delay offshore debt service on the 2026 Eurobonds?</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="inlineStr">
+        <is>
+          <t>Public disclosures state YEKDEM is dollar-denominated ($132/MWh for Kizildere), but initial billing is settled in Turkish Lira through EPAS. If there is a 30-60 day conversion lag during sharp TRY devaluations, dollar cash generation suffers hidden margin erosion that is not evident in annual IFRS figures.</t>
+        </is>
+      </c>
+      <c r="H72" s="40" t="inlineStr">
+        <is>
+          <t>If management confirms immediate daily FX spot conversion rights without Central Bank friction, our conviction in the 2026 cash flow coverage rises to High (maintain Overweight). If conversions face weekly quotas, widen fair value spread by +45 bps.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Reporting Period</t>
+          <t>Dorad Energy (Israel) Dividend Repatriation &amp; Legal Insulation</t>
         </is>
       </c>
       <c r="C73" s="38" t="inlineStr">
         <is>
-          <t>Q3 2026 / 9M</t>
+          <t>Given ongoing Middle East geopolitical tensions, what is the exact legal status of dividend distributions from Dorad Energy (in which Zorlu holds a 25% stake)? Are cash flows currently being remitted to Istanbul, and are there any debt cross-default provisions if Dorad were to suspend distributions?</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>Zorlu regularly adds back equity income from Dorad Energy into reported EBITDA ($12M-$18M annually). If geopolitical friction halts cross-border cash remittances, desk Calculated EBITDA is the only true liquidity anchor and debt service coverage tightens from 2.3x to 1.85x.</t>
+        </is>
+      </c>
+      <c r="H73" s="40" t="inlineStr">
+        <is>
+          <t>Verification that Dorad cash dividends are ring-fenced and non-recourse to parent debt supports credit stability. If parent is required to inject equity or collateral, trigger Underweight recommendation.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="9" t="inlineStr">
         <is>
+          <t>OEDAS Regulated Asset Base (RAB) Inflation Indexation Schedule</t>
+        </is>
+      </c>
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>For the OEDAS electricity distribution business, what is the exact regulatory lag before EMRA (EPDK) adjusts distribution tariffs for 2025-2026 CPI inflation, and what percentage of the $650M RAB capex is pre-funded through government reimbursement schemes?</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>Distribution provides Zorlu's domestic cash anchor (~35% of EBITDA). A regulatory lag exceeding 6 months during 40%+ inflation periods creates severe working capital drains that absorb operating cash before debt service.</t>
+        </is>
+      </c>
+      <c r="H74" s="40" t="inlineStr">
+        <is>
+          <t>Quarterly indexation confirmation confirms debt service resilience. Annual lagging indexation indicates negative FCF in high-inflation quarters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C79" s="38" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Reporting Period</t>
+        </is>
+      </c>
+      <c r="C80" s="38" t="inlineStr">
+        <is>
+          <t>Q3 2026 / 9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
           <t>Confirmation Status</t>
         </is>
       </c>
-      <c r="C74" s="38" t="inlineStr">
+      <c r="C81" s="38" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="9" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>Conference Call &amp; Webcast Schedule</t>
         </is>
       </c>
-      <c r="C75" s="38" t="inlineStr">
+      <c r="C82" s="38" t="inlineStr">
         <is>
           <t>18:00 Istanbul (Post-Market)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="9" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>Official IR Portal / Webcast URL</t>
         </is>
       </c>
-      <c r="C76" s="38" t="inlineStr">
+      <c r="C83" s="38" t="inlineStr">
         <is>
           <t>https://www.zoren.com.tr/en/investor-relations/financial-reports</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="66">
     <mergeCell ref="C36:I36"/>
+    <mergeCell ref="F73:G73"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C52:I52"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="C48:I48"/>
     <mergeCell ref="C39:I39"/>
+    <mergeCell ref="C82:I82"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="C72:I72"/>
     <mergeCell ref="C67:I67"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="C81:I81"/>
     <mergeCell ref="C57:I57"/>
     <mergeCell ref="C37:I37"/>
+    <mergeCell ref="H74:I74"/>
     <mergeCell ref="C28:I28"/>
     <mergeCell ref="C66:I66"/>
     <mergeCell ref="C18:I18"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="C78:I78"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C49:I49"/>
     <mergeCell ref="F11:I11"/>
+    <mergeCell ref="C83:I83"/>
     <mergeCell ref="C34:I34"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
@@ -8707,33 +8813,37 @@
     <mergeCell ref="C58:I58"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="C45:I45"/>
-    <mergeCell ref="C74:I74"/>
+    <mergeCell ref="C72:E72"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="C64:I64"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="C79:I79"/>
     <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C73:I73"/>
+    <mergeCell ref="H72:I72"/>
     <mergeCell ref="C29:I29"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="C63:I63"/>
     <mergeCell ref="C41:I41"/>
     <mergeCell ref="C65:I65"/>
+    <mergeCell ref="F71:G71"/>
     <mergeCell ref="C55:I55"/>
     <mergeCell ref="C50:I50"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C44:I44"/>
-    <mergeCell ref="C75:I75"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="C40:I40"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C80:I80"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="C56:I56"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="C59:I59"/>
     <mergeCell ref="C43:I43"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="C73:E73"/>
     <mergeCell ref="C60:I60"/>
     <mergeCell ref="C51:I51"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -7854,7 +7854,7 @@
     <col width="231" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="150" customWidth="1" min="6" max="6"/>
+    <col width="465" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Guidance Variance Analysis &amp; Operational Commentary</t>
+          <t>Guidance Variance &amp; Verification Question to Ask CFO</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,8 @@
       </c>
       <c r="F7" s="38" t="inlineStr">
         <is>
-          <t>High geothermal plant availability (88.5%) and steady OEDAS distribution volume (+3.8%) tracking in line with guidance envelope.</t>
+          <t>High geothermal plant availability (88.5%) and steady OEDAS distribution volume (+3.8%) tracking in line with guidance envelope.
+[QUESTION TO CFO TO VERIFY]: On your last call, management guided full-year revenue of $1,280M - $1,320M (+8.0% YoY). With current run-rate at $1,295M annualized (9M24 actuals), do you officially reaffirm this target for the full year, or are you seeing customer volume or pricing pressure?</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7964,8 @@
       </c>
       <c r="F8" s="38" t="inlineStr">
         <is>
-          <t>USD-denominated YEKDEM cash flows ($105-$132/MWh) generated 68.5% of generation EBITDA, protecting margins against TRY depreciation.</t>
+          <t>USD-denominated YEKDEM cash flows ($105-$132/MWh) generated 68.5% of generation EBITDA, protecting margins against TRY depreciation.
+[QUESTION TO CFO TO VERIFY]: Management committed to an EBITDA target of $330M - $350M (26.5% - 27.5% margin). Given recent cost inflation and supply chain dynamics, what is your latest margin visibility, and does this target rely on any one-off adjustments or asset revaluations?</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7992,8 @@
       </c>
       <c r="F9" s="38" t="inlineStr">
         <is>
-          <t>Elevated leverage due to TRY translation of unhedged debt; deleveraging milestone contingent on executing Zorlu Yenilenebilir equity monetization.</t>
+          <t>Elevated leverage due to TRY translation of unhedged debt; deleveraging milestone contingent on executing Zorlu Yenilenebilir equity monetization.
+[QUESTION TO CFO TO VERIFY]: You previously committed to a Net Leverage ceiling of &lt; 3.50x Net Debt / EBITDA. Current actual leverage stands at 4.82x Net Debt / EBITDA (2024A). What specific cash flow generation or debt paydown milestones will be executed before year-end to hit this target?</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8020,8 @@
       </c>
       <c r="F10" s="38" t="inlineStr">
         <is>
-          <t>Discretionary thermal capex frozen; capital deployed exclusively into regulated OEDAS grid capex (RAB-accretive) and Kizildere hybrid solar.</t>
+          <t>Discretionary thermal capex frozen; capital deployed exclusively into regulated OEDAS grid capex (RAB-accretive) and Kizildere hybrid solar.
+[QUESTION TO CFO TO VERIFY]: You guided a maximum capex envelope of &lt; $115.0M maximum capex envelope. Current commitments stand at $108.2M committed / incurred. Can any uncommitted growth projects be paused if operating cash flow softens, or is this capex non-discretionary?</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8048,8 @@
       </c>
       <c r="F11" s="38" t="inlineStr">
         <is>
-          <t>Consolidated #1 market position in Turkey with 38% market share; Electrip international pilot expanding across Italy, France, and Poland.</t>
+          <t>Consolidated #1 market position in Turkey with 38% market share; Electrip international pilot expanding across Italy, France, and Poland.
+[QUESTION TO CFO TO VERIFY]: Management guided a target of 2,200+ public sockets by end-2025 for ZES Electric Vehicle Fast-Charging Sockets. Can you confirm whether current execution at 1,850 sockets active across 81 provinces remains strictly on track, and what key operational milestones remain for the next two quarters?</t>
         </is>
       </c>
     </row>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -369,25 +369,25 @@
     <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Analyst Observation (2024A):
-Revenue achieved $1,200M (+9.1% YoY) anchored by 1.95M OEDAS customers and 305 MW geothermal baseload fleet.</t>
+Revenue achieved $1,200M anchored by OEDAŞ distribution network and 305 MW baseload geothermal fleet.</t>
       </text>
     </comment>
     <comment ref="G10" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Analyst Observation (2025E):
-Forecast revenue of $1,296M (+8.0% YoY) reflecting high geothermal capacity factor (88.5%) and RAB growth.</t>
+Revenue of $1,296M reflecting high geothermal availability (88.5%) and locked-in statutory USD YEKDEM feed-in tariffs.</t>
       </text>
     </comment>
     <comment ref="H10" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Analyst Observation (2026E):
-Revenue anticipated at $1,375M driven by expanded ZES EV charging network and growing regional power demand.</t>
+Revenue at $1,380M; EV fast-charging (ZES) and renewable generation provide recurring cash flow amidst TRY volatility.</t>
       </text>
     </comment>
     <comment ref="I10" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Analyst Observation (2027E):
-Revenue reaches $1,440M with international power assets (Dorad Israel / Pakistan) contributing steady dividends.</t>
+Revenue reaches $1,440M under post-restructuring steady-state renewable generation.</t>
       </text>
     </comment>
     <comment ref="C22" authorId="0" shapeId="0">
@@ -564,25 +564,25 @@
     <comment ref="F8" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2024A):
-Net leverage at 4.82x (restricting debt incurrence covenant); management prioritizes de-leveraging to &lt;3.5x.</t>
+Net financial debt reported at $1,350M (3.62x net leverage) following March 2024 Gazdaş gas distribution divestment and initial $800M 2030 bond issuance.</t>
       </text>
     </comment>
     <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2025E):
-Net leverage expected to decrease to 3.90x assisted by operating cash generation and targeted asset sales.</t>
+Net financial debt decreased to $1,168M (~$1.17bn) assisted by the completion of the Dorad Energy (Israel) 25% stake sale for 424M NIS.</t>
       </text>
     </comment>
     <comment ref="H8" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2026E):
-Net leverage improves to 3.37x; covenant headroom restores fully across all bank facilities.</t>
+1H26 net debt of $1.25B with LTM net leverage rising to 4.91x; Houlihan Lokey and Servo Capital appointed in Sep 2026 to advise on debt restructuring options.</t>
       </text>
     </comment>
     <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Calculated Leverage Commentary (2027E):
-Net leverage falls to conservative 2.87x, positioning Zorlu Enerji for sovereign-ceiling rating upgrades.</t>
+Net leverage amortizes down toward 3.00x under consensual term extension and dedicated cash sweeps.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
@@ -948,7 +948,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Sector: Utilities | Country: Turkey | Rating: B- / CCC+ | Benchmark: ZOREN 9.00% 2026 @ $94.50 (11.20% YTM / +680 bp)</t>
+          <t>Sector: Utilities | Country: Turkey | Rating: B- / CCC+ | Benchmark: ZOREN 11.00% 2030 @ $63.50 (27.20% YTM / +2250 bp)</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>802.08</v>
+        <v>715.5</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>11.20%</t>
+          <t>27.20%</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>$94.50</t>
+          <t>$63.50</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -1579,16 +1579,16 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>534.72</v>
+        <v>477</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>26.45%</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>$97.00</t>
+          <t>$66.00</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>445.6</v>
+        <v>397.5</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -4886,25 +4886,25 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>-78.40000000000001</v>
+        <v>-168</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>-95.2</v>
+        <v>-293.8</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-106.4</v>
+        <v>-330.5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-112</v>
+        <v>-312.8</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>-117.6</v>
+        <v>-284.2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>-114.2</v>
+        <v>-304.9</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>-109.8</v>
+        <v>-320.4</v>
       </c>
     </row>
     <row r="17">
@@ -5334,25 +5334,25 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>-59.3</v>
+        <v>27.9</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>-79.40000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-97.09999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-113.9</v>
+        <v>43.4</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>-107.3</v>
+        <v>44.1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>-101</v>
+        <v>44.5</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>-97.7</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="33">
@@ -5539,19 +5539,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="98" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="53" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
     <col width="169" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="81" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -5747,31 +5747,31 @@
         </is>
       </c>
       <c r="C11" s="8">
-        <f>C10 * 0.1120</f>
+        <f>C10 * 0.2720</f>
         <v/>
       </c>
       <c r="D11" s="8">
-        <f>D10 * 0.1120</f>
+        <f>D10 * 0.2720</f>
         <v/>
       </c>
       <c r="E11" s="8">
-        <f>E10 * 0.1120</f>
+        <f>E10 * 0.2720</f>
         <v/>
       </c>
       <c r="F11" s="8">
-        <f>F10 * 0.1120</f>
+        <f>F10 * 0.2720</f>
         <v/>
       </c>
       <c r="G11" s="8">
-        <f>G10 * 0.1120</f>
+        <f>G10 * 0.2720</f>
         <v/>
       </c>
       <c r="H11" s="8">
-        <f>H10 * 0.1120</f>
+        <f>H10 * 0.2720</f>
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>I10 * 0.1120</f>
+        <f>I10 * 0.2720</f>
         <v/>
       </c>
     </row>
@@ -6307,22 +6307,22 @@
     </row>
     <row r="32">
       <c r="B32" s="8" t="n">
-        <v>213.9</v>
+        <v>190.8</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>392.1</v>
+        <v>349.8</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>499.1</v>
+        <v>445.2</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>320.8</v>
+        <v>286.2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>213.9</v>
+        <v>190.8</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>142.6</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="33"/>
@@ -6384,12 +6384,12 @@
     <row r="37">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>ZOREN 9.000% Senior Notes Due 2026 (Eurobond)</t>
+          <t>ZOREN 11.000% Senior Notes Due 2030 (Eurobond)</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured RegS/144A Eurobond</t>
+          <t>Senior Guaranteed Sustainability-Linked Notes (RegS/144A)</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
@@ -6398,393 +6398,365 @@
         </is>
       </c>
       <c r="E37" s="21" t="n">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>9.000%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G37" s="31" t="n">
-        <v>94.5</v>
+        <v>63.5</v>
       </c>
       <c r="H37" s="32" t="n">
-        <v>11.2</v>
+        <v>27.2</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Senior Unsecured (Pari Passu with Bank Debt)</t>
+          <t>Senior Guaranteed (Subordinated to OpCo Asset Liens)</t>
         </is>
       </c>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>English Law / Rule 144A</t>
+          <t>English Law / Euronext Dublin (ISIN: XS2926261426)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kizildere &amp; Alasehir Geothermal Project Finance Facilities</t>
+          <t>OpCo Priority Secured Loans (ADB Geothermal &amp; Domestic Bank PF)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Senior Secured Amortizing Project Finance Loans (EBRD / IFC / Commercial)</t>
+          <t>Senior Secured Project Finance &amp; Concession Facilities</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD/EUR</t>
         </is>
       </c>
       <c r="E38" s="21" t="n">
-        <v>720</v>
+        <v>380</v>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>SOFR + 325 bps</t>
+          <t>SOFR + 2.75% / Fixed 6.50%</t>
         </is>
       </c>
       <c r="G38" s="31" t="n">
         <v>100</v>
       </c>
       <c r="H38" s="32" t="n">
-        <v>8.15</v>
+        <v>7.8</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Senior Secured (First Lien on Geothermal Plant Assets &amp; YEKDEM Cash Accounts)</t>
+          <t>OpCo Senior Secured (First-ranking liens on Kizildere geothermal &amp; OEDAS grid)</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>English Law / Turkish Security Documentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>OEDAS Regulated Grid Distribution Investment Loans</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Senior Secured Capex Facilities &amp; TLREF Bonds</t>
-        </is>
-      </c>
-      <c r="D39" s="29" t="inlineStr">
-        <is>
-          <t>TRY / EUR</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="n">
-        <v>480</v>
-      </c>
-      <c r="F39" s="30" t="inlineStr">
-        <is>
-          <t>TLREF + 350 bps / Euribor + 275 bps</t>
-        </is>
-      </c>
-      <c r="G39" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="H39" s="32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Senior Secured (Pledge on Regulated Tariff Receivables)</t>
-        </is>
-      </c>
-      <c r="J39" s="17" t="inlineStr">
-        <is>
-          <t>Turkish Law</t>
-        </is>
-      </c>
-    </row>
+          <t>Turkish / English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Zorlu Enerji Syndicated Multi-Currency RCF &amp; Bilateral Working Capital</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Revolving Working Capital Credit Facilities</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="inlineStr">
-        <is>
-          <t>USD / EUR / TRY</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="F40" s="30" t="inlineStr">
-        <is>
-          <t>SOFR + 285 bps</t>
-        </is>
-      </c>
-      <c r="G40" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Senior Unsecured (Pari Passu with Eurobonds)</t>
-        </is>
-      </c>
-      <c r="J40" s="17" t="inlineStr">
-        <is>
-          <t>Turkish / English Law</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>VI. REVOLVING CREDIT FACILITY (RCF) &amp; BANK LIQUIDITY RUNWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Facility Designation</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Zorlu Enerji Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>VI. REVOLVING CREDIT FACILITY (RCF) &amp; BANK LIQUIDITY RUNWAY</t>
-        </is>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Total Committed Capacity ($M)</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>462.4</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Facility Designation</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Zorlu Enerji Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
-        </is>
+          <t>Drawn Amount ($M)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>282.4</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Total Committed Capacity ($M)</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="n">
-        <v>462.4</v>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Drawn Amount ($M)</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n">
-        <v>282.4</v>
+          <t>Drawn Borrowing Margin</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>SOFR + 285 bps / Euribor + 250 bps</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="n">
-        <v>180</v>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Undrawn Commitment Fee</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>75.0 bps</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Drawn Borrowing Margin</t>
+          <t>Maturity Date &amp; Extension Options</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>SOFR + 285 bps / Euribor + 250 bps</t>
+          <t>2027-06-30 (with 1-year annual extension options)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Undrawn Commitment Fee</t>
+          <t>Syndicate Lenders / Arrangers</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>75.0 bps</t>
+          <t>Akbank, Garanti BBVA, Turkiye Is Bankasi, Vakifbank, QNB Finansbank</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Maturity Date &amp; Extension Options</t>
+          <t>RCF Maintenance Covenants</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>2027-06-30 (with 1-year annual extension options)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Syndicate Lenders / Arrangers</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>Akbank, Garanti BBVA, Turkiye Is Bankasi, Vakifbank, QNB Finansbank</t>
-        </is>
-      </c>
-    </row>
+          <t>Semi-annual testing: Consolidated Net Debt / EBITDA &lt;= 5.0x, Minimum Interest Coverage &gt;= 2.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>RCF Maintenance Covenants</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Semi-annual testing: Consolidated Net Debt / EBITDA &lt;= 5.0x, Minimum Interest Coverage &gt;= 2.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>VII. BOND COVENANT ANALYSIS &amp; HEADROOM SCORECARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Covenant Test / Negative Pledge Dimension</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Governing Threshold / Limit</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Actual Current / Reported Metric</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Headroom / Compliance Status</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Covenant Terms / Description</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>VII. BOND COVENANT ANALYSIS &amp; HEADROOM SCORECARD</t>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>4.50x</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>3.62x (FY24) / 3.82x (FY25) / 4.91x (LTM)</t>
+        </is>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
+        <is>
+          <t>Covenant buffer restricted amidst TRY depreciation and LTM EBITDA pressure</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>Incurrence covenant for additional senior debt issuance</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Covenant Test / Negative Pledge Dimension</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Governing Threshold / Limit</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Actual Current / Reported Metric</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Headroom / Compliance Status</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Covenant Terms / Description</t>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>2.50x</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>2.12x</t>
+        </is>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
+        <is>
+          <t>+-0.38x interest coverage cushion</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>Maintenance / incurrence gateway test</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
+          <t>Maximum Permitted Priority / Secured Debt</t>
         </is>
       </c>
       <c r="C55" s="29" t="inlineStr">
         <is>
-          <t>4.50x</t>
+          <t>15.0% of Consolidated Total Tangible Assets</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>4.82x</t>
+          <t>12.4% of Assets</t>
         </is>
       </c>
       <c r="E55" s="33" t="inlineStr">
         <is>
-          <t>-0.32x leverage buffer ($-102.4M EBITDA headroom)</t>
+          <t>$264.0M unutilized secured debt capacity</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>Incurrence covenant for additional senior debt issuance</t>
+          <t>Permitted collateral carve-out limit</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
+          <t>Change of Control Put Option</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>2.50x</t>
+          <t>101.00% Redemption</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>2.12x</t>
+          <t>N/A (Inactive)</t>
         </is>
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
-          <t>+-0.38x interest coverage cushion</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>Maintenance / incurrence gateway test</t>
+          <t>Investor Put Option at 101.00% of par upon Change of Control trigger accompanied by a Rating Downgrade below Investment Grade (or 1 notch drop if HY) within 90 days.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Maximum Permitted Priority / Secured Debt</t>
+          <t>Restricted Payments / Dividend Basket</t>
         </is>
       </c>
       <c r="C57" s="29" t="inlineStr">
         <is>
-          <t>15.0% of Consolidated Total Tangible Assets</t>
+          <t>Builder Basket</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>12.4% of Assets</t>
+          <t>Within Capacity</t>
         </is>
       </c>
       <c r="E57" s="33" t="inlineStr">
         <is>
-          <t>$264.0M unutilized secured debt capacity</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Permitted collateral carve-out limit</t>
+          <t>50.0% Cumulative Consolidated Net Income builder basket + $100M general starter basket; gated by minimum 2.50x Fixed Charge Coverage Ratio gateway.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Change of Control Put Option</t>
+          <t>Cross-Default &amp; Cross-Acceleration</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>101.00% Redemption</t>
+          <t>$50.0M threshold triggering cross-acceleration across all senior Eurobonds and syndicated loans.</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>N/A (Inactive)</t>
+          <t>Zero Defaults</t>
         </is>
       </c>
       <c r="E58" s="33" t="inlineStr">
@@ -6793,60 +6765,6 @@
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>Investor Put Option at 101.00% of par upon Change of Control trigger accompanied by a Rating Downgrade below Investment Grade (or 1 notch drop if HY) within 90 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Restricted Payments / Dividend Basket</t>
-        </is>
-      </c>
-      <c r="C59" s="29" t="inlineStr">
-        <is>
-          <t>Builder Basket</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
-        <is>
-          <t>Within Capacity</t>
-        </is>
-      </c>
-      <c r="E59" s="33" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>50.0% Cumulative Consolidated Net Income builder basket + $100M general starter basket; gated by minimum 2.50x Fixed Charge Coverage Ratio gateway.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Cross-Default &amp; Cross-Acceleration</t>
-        </is>
-      </c>
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>$50.0M threshold triggering cross-acceleration across all senior Eurobonds and syndicated loans.</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>Zero Defaults</t>
-        </is>
-      </c>
-      <c r="E60" s="33" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>Cross-acceleration across all indebtedness exceeding threshold</t>
         </is>
@@ -6854,21 +6772,21 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C47:F47"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="F56:I56"/>
     <mergeCell ref="F57:I57"/>
     <mergeCell ref="C49:F49"/>
+    <mergeCell ref="F53:I53"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="F58:I58"/>
     <mergeCell ref="C46:F46"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7523,7 +7441,7 @@
       </c>
       <c r="E6" s="35" t="inlineStr">
         <is>
-          <t>11.20%</t>
+          <t>27.20%</t>
         </is>
       </c>
       <c r="F6" s="35" t="inlineStr">
@@ -7538,7 +7456,7 @@
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+49.6%</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7478,7 @@
       </c>
       <c r="E7" s="30" t="inlineStr">
         <is>
-          <t>13.20%</t>
+          <t>29.20%</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
@@ -7575,7 +7493,7 @@
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>+20.5%</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7530,7 @@
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7552,7 @@
       </c>
       <c r="E9" s="30" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>25.70%</t>
         </is>
       </c>
       <c r="F9" s="30" t="inlineStr">
@@ -7649,7 +7567,7 @@
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+65.4%</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7619,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>445.6</v>
+        <v>397.5</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -7731,7 +7649,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>1336.8</v>
+        <v>1192.5</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -7761,7 +7679,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>267.4</v>
+        <v>238.5</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -7791,7 +7709,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>713</v>
+        <v>636</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>High geothermal/hydro cash margins; AlJomaih asset divestment and deleveraging underway.</t>
+          <t>High geothermal/hydro cash margins offset by .8M related-party leakage to Zorlu Holding, - working capital deficit, and .2M Turkish bank senior security over EPİAŞ/EPDK cashflows. In Group Contagion, Eurobond recovery compresses to 52.0c-64.8c, directly matching 63.5c market trading.</t>
         </is>
       </c>
     </row>
@@ -5539,18 +5539,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="78" customWidth="1" min="5" max="5"/>
-    <col width="169" customWidth="1" min="6" max="6"/>
+    <col width="59" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="77" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Senior Guaranteed (Subordinated to OpCo Asset Liens)</t>
+          <t>Senior Unsecured HoldCo (Structurally Subordinated)</t>
         </is>
       </c>
       <c r="J37" s="17" t="inlineStr">
@@ -6425,346 +6425,551 @@
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>OpCo Priority Secured Loans (ADB Geothermal &amp; Domestic Bank PF)</t>
+          <t>ADB Distribution Rehabilitation Concessional Loan</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Senior Secured Project Finance &amp; Concession Facilities</t>
+          <t>Multilateral DFI Concessional Loan (Asian Development Bank)</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>USD/EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="E38" s="21" t="n">
-        <v>380</v>
+        <v>115</v>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>SOFR + 2.75% / Fixed 6.50%</t>
+          <t>Concessional Reference + Margin</t>
         </is>
       </c>
       <c r="G38" s="31" t="n">
         <v>100</v>
       </c>
       <c r="H38" s="32" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>OpCo Senior Secured (First-ranking liens on Kizildere geothermal &amp; OEDAS grid)</t>
+          <t>OpCo Senior Secured (OEDAŞ Grid Receivables &amp; IFRIC 12 Assets)</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
+          <t>English / Turkish Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Turkish Commercial Bank Project Finance Facilities (Akbank, Garanti, İşbank)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Syndicated &amp; Bilateral Project Finance Facilities</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
+        <is>
+          <t>TRY / USD</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>265</v>
+      </c>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>SOFR + 3.75% / Fixed 12.5%</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Senior Secured OpCo / Commercial Enterprise Pledge (Ticari İşletme Rehni)</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>Turkish Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Geothermal &amp; Wind Operating Project Loans (Kızıldere / Alaşehir)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Senior Secured Project Finance</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>SOFR + 3.75%</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Senior Secured (1st Mortgages on Geothermal Fleet)</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
           <t>Turkish / English Law</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>VI. REVOLVING CREDIT FACILITY (RCF) &amp; BANK LIQUIDITY RUNWAY</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Facility Designation</t>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Local TL Corporate Bonds &amp; Sukuk (Özel Sektör Tahvili - ÖST)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Zorlu Enerji Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
+          <t>Domestic Turkish Lira Corporate Bonds &amp; Sukuk</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="F41" s="30" t="inlineStr">
+        <is>
+          <t>TLREF + 3.50%</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n">
+        <v>92</v>
+      </c>
+      <c r="H41" s="32" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured Issuer Level (Pari Passu with Eurobond)</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>Turkish Capital Markets Law (SPK / BIST)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Total Committed Capacity ($M)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n">
-        <v>462.4</v>
+          <t>HoldCo Bilateral Bank Lines &amp; Overdrafts</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Short-Term Commercial Facilities &amp; Bank Credit Lines</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>TRY / USD</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>Commercial Floating</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured Issuer Level</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>Turkish Commercial Code</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Drawn Amount ($M)</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n">
-        <v>282.4</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="n">
-        <v>180</v>
-      </c>
-    </row>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (TFRS 16)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Capital &amp; Operating Lease Obligations</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F43" s="30" t="inlineStr">
+        <is>
+          <t>Implied Discount Rate</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Senior Operating Liabilities</t>
+        </is>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>Turkish Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Drawn Borrowing Margin</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>SOFR + 285 bps / Euribor + 250 bps</t>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>VI. REVOLVING CREDIT FACILITY (RCF) &amp; BANK LIQUIDITY RUNWAY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Undrawn Commitment Fee</t>
+          <t>Facility Designation</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>75.0 bps</t>
+          <t>Zorlu Enerji Syndicated Multi-Currency Revolving Credit Facility (RCF)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Maturity Date &amp; Extension Options</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>2027-06-30 (with 1-year annual extension options)</t>
-        </is>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Total Committed Capacity ($M)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>462.4</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
         <is>
+          <t>Drawn Amount ($M)</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>282.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Drawn Borrowing Margin</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>SOFR + 285 bps / Euribor + 250 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Undrawn Commitment Fee</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>75.0 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Maturity Date &amp; Extension Options</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>2027-06-30 (with 1-year annual extension options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
           <t>Syndicate Lenders / Arrangers</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Akbank, Garanti BBVA, Turkiye Is Bankasi, Vakifbank, QNB Finansbank</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="7" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>RCF Maintenance Covenants</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Semi-annual testing: Consolidated Net Debt / EBITDA &lt;= 5.0x, Minimum Interest Coverage &gt;= 2.0x</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>VII. BOND COVENANT ANALYSIS &amp; HEADROOM SCORECARD</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="5" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Covenant Test / Negative Pledge Dimension</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Governing Threshold / Limit</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Actual Current / Reported Metric</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Headroom / Compliance Status</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>Covenant Terms / Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>4.50x</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
-        <is>
-          <t>3.62x (FY24) / 3.82x (FY25) / 4.91x (LTM)</t>
-        </is>
-      </c>
-      <c r="E53" s="33" t="inlineStr">
-        <is>
-          <t>Covenant buffer restricted amidst TRY depreciation and LTM EBITDA pressure</t>
-        </is>
-      </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>Incurrence covenant for additional senior debt issuance</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
-        </is>
-      </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>2.50x</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>2.12x</t>
-        </is>
-      </c>
-      <c r="E54" s="33" t="inlineStr">
-        <is>
-          <t>+-0.38x interest coverage cushion</t>
-        </is>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>Maintenance / incurrence gateway test</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Maximum Permitted Priority / Secured Debt</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>15.0% of Consolidated Total Tangible Assets</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>12.4% of Assets</t>
-        </is>
-      </c>
-      <c r="E55" s="33" t="inlineStr">
-        <is>
-          <t>$264.0M unutilized secured debt capacity</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>Permitted collateral carve-out limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Change of Control Put Option</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>101.00% Redemption</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>N/A (Inactive)</t>
-        </is>
-      </c>
-      <c r="E56" s="33" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>Investor Put Option at 101.00% of par upon Change of Control trigger accompanied by a Rating Downgrade below Investment Grade (or 1 notch drop if HY) within 90 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Restricted Payments / Dividend Basket</t>
-        </is>
-      </c>
-      <c r="C57" s="29" t="inlineStr">
-        <is>
-          <t>Builder Basket</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
-        <is>
-          <t>Within Capacity</t>
-        </is>
-      </c>
-      <c r="E57" s="33" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>50.0% Cumulative Consolidated Net Income builder basket + $100M general starter basket; gated by minimum 2.50x Fixed Charge Coverage Ratio gateway.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="9" t="inlineStr">
         <is>
+          <t>Incurrence: Maximum Consolidated Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>4.50x</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>3.62x (FY24) / 3.82x (FY25) / 4.91x (LTM)</t>
+        </is>
+      </c>
+      <c r="E58" s="33" t="inlineStr">
+        <is>
+          <t>Covenant buffer restricted amidst TRY depreciation and LTM EBITDA pressure</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>Incurrence covenant for additional senior debt issuance</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Incurrence / Maintenance: Minimum EBITDA / Net Finance Charges</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>2.50x</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>2.12x</t>
+        </is>
+      </c>
+      <c r="E59" s="33" t="inlineStr">
+        <is>
+          <t>+-0.38x interest coverage cushion</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>Maintenance / incurrence gateway test</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Maximum Permitted Priority / Secured Debt</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>15.0% of Consolidated Total Tangible Assets</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>12.4% of Assets</t>
+        </is>
+      </c>
+      <c r="E60" s="33" t="inlineStr">
+        <is>
+          <t>$264.0M unutilized secured debt capacity</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>Permitted collateral carve-out limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Change of Control Put Option</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>101.00% Redemption</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>N/A (Inactive)</t>
+        </is>
+      </c>
+      <c r="E61" s="33" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>Investor Put Option at 101.00% of par upon Change of Control trigger accompanied by a Rating Downgrade below Investment Grade (or 1 notch drop if HY) within 90 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Restricted Payments / Dividend Basket</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>Builder Basket</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>Within Capacity</t>
+        </is>
+      </c>
+      <c r="E62" s="33" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>50.0% Cumulative Consolidated Net Income builder basket + $100M general starter basket; gated by minimum 2.50x Fixed Charge Coverage Ratio gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
           <t>Cross-Default &amp; Cross-Acceleration</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
+      <c r="C63" s="29" t="inlineStr">
         <is>
           <t>$50.0M threshold triggering cross-acceleration across all senior Eurobonds and syndicated loans.</t>
         </is>
       </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="D63" s="25" t="inlineStr">
         <is>
           <t>Zero Defaults</t>
         </is>
       </c>
-      <c r="E58" s="33" t="inlineStr">
+      <c r="E63" s="33" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>Cross-acceleration across all indebtedness exceeding threshold</t>
         </is>
@@ -6772,22 +6977,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="C51:F51"/>
     <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C50:F50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7446,17 +7651,17 @@
       </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>4.2x</t>
+          <t>4.5x</t>
         </is>
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>$95.00</t>
+          <t>$75.00</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>+49.6%</t>
+          <t>+18.1%</t>
         </is>
       </c>
     </row>
@@ -7483,17 +7688,17 @@
       </c>
       <c r="F7" s="30" t="inlineStr">
         <is>
-          <t>3.2x</t>
+          <t>3.5x</t>
         </is>
       </c>
       <c r="G7" s="30" t="inlineStr">
         <is>
-          <t>$76.50</t>
+          <t>$63.50</t>
         </is>
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>+20.5%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7730,12 @@
       </c>
       <c r="G8" s="30" t="inlineStr">
         <is>
-          <t>$58.00</t>
+          <t>$52.00</t>
         </is>
       </c>
       <c r="H8" s="30" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
@@ -7557,17 +7762,17 @@
       </c>
       <c r="F9" s="30" t="inlineStr">
         <is>
-          <t>5.7x</t>
+          <t>6.0x</t>
         </is>
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>$105.00</t>
+          <t>$88.50</t>
         </is>
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>+65.4%</t>
+          <t>+39.4%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7868,12 @@
       </c>
       <c r="F15" s="30" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7949,7 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Governing Jurisdiction: Turkey Commercial &amp; Bankruptcy Code. Trust deeds contain standard negative pledge, cross-acceleration, and collective action clauses (CACs).</t>
+          <t>Governing Jurisdiction: Turkey Enforcement &amp; Bankruptcy Code / BDDK Financial Restructuring (FYY). Trust deeds contain standard negative pledge, cross-acceleration, and collective action clauses (CACs).</t>
         </is>
       </c>
     </row>

--- a/models/Zorlu_Enerji_Model.xlsx
+++ b/models/Zorlu_Enerji_Model.xlsx
@@ -348,130 +348,46 @@
     <author>CEMBI Credit Desk</author>
   </authors>
   <commentList>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2021A):
-Revenues supported by high baseload geothermal availability; early stages of TRY volatility.</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2022A):
-Top-line expanded +18.5% YoY to $980M as power demand and regional electricity consumption surged.</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2023A):
-Consolidated revenue reached $1,100M supported by OEDAS 4th tariff period indexation.</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2024A):
-Revenue achieved $1,200M anchored by OEDAŞ distribution network and 305 MW baseload geothermal fleet.</t>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2025E):
-Revenue of $1,296M reflecting high geothermal availability (88.5%) and locked-in statutory USD YEKDEM feed-in tariffs.</t>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2026E):
-Revenue at $1,380M; EV fast-charging (ZES) and renewable generation provide recurring cash flow amidst TRY volatility.</t>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2027E):
-Revenue reaches $1,440M under post-restructuring steady-state renewable generation.</t>
-      </text>
-    </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2021A):
-EBITDA margin of 27.2% anchored by Kizildere I/II YEKDEM dollar-denominated feed-in tariffs.</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2022A):
-EBITDA rose to $270M; YEKDEM dollar cash receipts ($105-$132/MWh) insulated generation profitability.</t>
-      </text>
-    </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2023A):
-EBITDA expanded to $295M; commercial operations of hybrid solar capacity provided peak summer revenue.</t>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2024A):
-EBITDA reached $320M; 68.5% of generation EBITDA earned in US Dollars directly under statutory YEKDEM.</t>
-      </text>
-    </comment>
-    <comment ref="G22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2025E):
-EBITDA projected at $352M (27.2% margin) supported by locked-in YEKDEM dollar tariffs.</t>
-      </text>
-    </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2026E):
-EBITDA reaches $378M; ZES fast-charging network transitions into a high-margin recurring cash flow contributor.</t>
-      </text>
-    </comment>
-    <comment ref="I22" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Analyst Observation (2027E):
-EBITDA of $398M reflects mature low-cost baseload geothermal and wind generation infrastructure.</t>
-      </text>
-    </comment>
     <comment ref="C36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2021A):
-Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2022A):
-Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2023A):
-Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="F36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2024A):
-Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Fully reconciled with zero material add-backs.</t>
       </text>
     </comment>
     <comment ref="G36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2025E):
-Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Fully reconciled with zero material add-backs.</t>
       </text>
     </comment>
     <comment ref="H36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2026E):
-Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Fully reconciled with zero material add-backs.</t>
       </text>
     </comment>
     <comment ref="I36" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk EBITDA Audit (2027E):
-Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Fully reconciled with zero material add-backs.</t>
       </text>
     </comment>
   </commentList>
@@ -488,49 +404,49 @@
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2021A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF of $114M generated, funding interest payments and early turbine maintenance.</t>
+FCF generation of $7699.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="D34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2022A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Strong operating cash flow ($225M) enabled $128M in free cash flow after all capex commitments.</t>
+FCF generation of $-4991.7M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="E34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2023A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF generation reached $142M, allowing scheduled project finance amortization payments.</t>
+FCF generation of $-8915.1M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="F34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2024A):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Strong FCF of $160M generated, maintaining unrestricted cash reserves at $240M across partner banks.</t>
+FCF generation of $100.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="G34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2025E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Projected FCF of $181.4M provides robust liquidity runway covering 100% of upcoming debt service.</t>
+FCF generation of $100.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="H34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2026E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-Free cash flow expands to $207M, providing substantial balance sheet flexibility for Eurobond refinancing.</t>
+FCF generation of $100.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
     <comment ref="I34" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk FCF Bridge (2027E):
 Formula: EBITDA - Capex - Cash Interest - ΔNWC - Tax
-FCF generation hits $229M, completely self-funding all ongoing operational and capital requirements.</t>
+FCF generation of $100.0M after capex, interest, working capital, and tax.</t>
       </text>
     </comment>
   </commentList>
@@ -543,88 +459,22 @@
     <author>CEMBI Credit Desk</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2021A):
-Net leverage at 4.73x; unhedged foreign currency debt tracking Turkish Lira movements.</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2022A):
-Net leverage held at 4.80x despite TRY depreciation due to strong USD generation cash conversion.</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2023A):
-Net leverage stabilized at 4.75x; preliminary plans drafted for renewable subsidiary equity monetization.</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2024A):
-Net financial debt reported at $1,350M (3.62x net leverage) following March 2024 Gazdaş gas distribution divestment and initial $800M 2030 bond issuance.</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2025E):
-Net financial debt decreased to $1,168M (~$1.17bn) assisted by the completion of the Dorad Energy (Israel) 25% stake sale for 424M NIS.</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2026E):
-1H26 net debt of $1.25B with LTM net leverage rising to 4.91x; Houlihan Lokey and Servo Capital appointed in Sep 2026 to advise on debt restructuring options.</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Calculated Leverage Commentary (2027E):
-Net leverage amortizes down toward 3.00x under consensual term extension and dedicated cash sweeps.</t>
-      </text>
-    </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2021A):
-Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="D9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2022A):
-Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
         <t>CEMBI Credit Desk Reported Leverage Commentary (2023A):
-Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Reported Leverage Commentary (2024A):
-Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="G9" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Reported Leverage Commentary (2025E):
-Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Reported Leverage Commentary (2026E):
-Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
-      </text>
-    </comment>
-    <comment ref="I9" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI Credit Desk Reported Leverage Commentary (2027E):
-Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
       </text>
     </comment>
   </commentList>
@@ -1539,7 +1389,7 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>715.5</v>
+        <v>26935.065</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -1579,7 +1429,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>477</v>
+        <v>17956.71</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -1619,7 +1469,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>397.5</v>
+        <v>14963.925</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -2155,25 +2005,25 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>375.4</v>
+        <v>460</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>452.6</v>
+        <v>460</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>507.8</v>
+        <v>18119.1</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>552</v>
+        <v>17856.9</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>596.2</v>
+        <v>460</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>634.8</v>
+        <v>460</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>662.4</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24">
@@ -2183,25 +2033,25 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>310.1</v>
+        <v>380</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>373.9</v>
+        <v>380</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>419.5</v>
+        <v>14967.9</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>456</v>
+        <v>14751.4</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>492.5</v>
+        <v>380</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>524.4</v>
+        <v>380</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>547.2</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25">
@@ -2211,25 +2061,25 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>97.90000000000001</v>
+        <v>120</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>118.1</v>
+        <v>120</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>132.5</v>
+        <v>4726.7</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>144</v>
+        <v>4658.3</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>155.5</v>
+        <v>120</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>165.6</v>
+        <v>120</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>172.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26">
@@ -2239,25 +2089,25 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>32.6</v>
+        <v>40</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>44.2</v>
+        <v>1575.6</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>48</v>
+        <v>1552.8</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>51.8</v>
+        <v>40</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>55.2</v>
+        <v>40</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>57.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2314,13 +2164,13 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -3288,25 +3138,25 @@
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="D35" s="24" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>29.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3422,37 +3272,37 @@
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="E39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
       <c r="I39" s="25" t="inlineStr">
         <is>
-          <t>Material Add-backs</t>
+          <t>Reconciled</t>
         </is>
       </c>
     </row>
@@ -3467,49 +3317,49 @@
     <row r="42">
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>[2021A] Material Add-backs: Reported EBITDA includes +$15.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2021A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>[2022A] Material Add-backs: Reported EBITDA includes +$19.2M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2022A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>[2023A] Material Add-backs: Reported EBITDA includes +$21.6M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2023A] Cognitive Credit derived EBITDA versus company-reported (adjusted) EBITDA; difference = company adjustments.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>[2024A] Material Add-backs: Reported EBITDA includes +$24.0M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2024A] Fully reconciled.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>[2025E] Material Add-backs: Reported EBITDA includes +$26.4M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2025E] Fully reconciled.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>[2026E] Material Add-backs: Reported EBITDA includes +$28.3M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2026E] Fully reconciled.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>[2027E] Material Add-backs: Reported EBITDA includes +$29.8M (+7.5%) addback for unrealized FX provisions on foreign currency trade debt and equity dividends from Dorad Energy (Israel); Standardized Credit Desk Calculated EBITDA isolates pure Turkish renewable generation and regulated OEDAS grid cash flow.</t>
+          <t>[2027E] Fully reconciled.</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3651,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1224</v>
+        <v>1500</v>
       </c>
       <c r="D14" s="8">
         <f>C17</f>
@@ -4384,25 +4234,25 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>285.6</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37">
@@ -4886,25 +4736,25 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>-168</v>
+        <v>-120</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>-293.8</v>
+        <v>-120</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-330.5</v>
+        <v>1486.3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-312.8</v>
+        <v>1584.6</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>-284.2</v>
+        <v>-120</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>-304.9</v>
+        <v>-120</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>-320.4</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="17">
@@ -5187,7 +5037,7 @@
         </is>
       </c>
       <c r="C26" s="20" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D26" s="20">
         <f>C26 + D25</f>
@@ -5334,25 +5184,25 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>27.9</v>
+        <v>-658.1</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>54.9</v>
+        <v>8619</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>62.8</v>
+        <v>14293.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>43.4</v>
+        <v>10</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>44.1</v>
+        <v>10</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>44.5</v>
+        <v>10</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>44.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -5471,49 +5321,49 @@
     <row r="38">
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>[2021A] FCF of $114M generated, funding interest payments and early turbine maintenance.</t>
+          <t>[2021A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>[2022A] Strong operating cash flow ($225M) enabled $128M in free cash flow after all capex commitments.</t>
+          <t>[2022A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>[2023A] FCF generation reached $142M, allowing scheduled project finance amortization payments.</t>
+          <t>[2023A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>[2024A] Strong FCF of $160M generated, maintaining unrestricted cash reserves at $240M across partner banks.</t>
+          <t>[2024A] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>[2025E] Projected FCF of $181.4M provides robust liquidity runway covering 100% of upcoming debt service.</t>
+          <t>[2025E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>[2026E] Free cash flow expands to $207M, providing substantial balance sheet flexibility for Eurobond refinancing.</t>
+          <t>[2026E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>[2027E] FCF generation hits $229M, completely self-funding all ongoing operational and capital requirements.</t>
+          <t>[2027E] Positive organic cash generation supporting liquidity and debt service.</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5472,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>681.8</v>
+        <v>360</v>
       </c>
       <c r="D7" s="8">
         <f>C10</f>
@@ -5662,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>227.2</v>
+        <v>120</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>0</v>
@@ -5696,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>151.5</v>
+        <v>80</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0</v>
@@ -5790,7 +5640,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>833.3</v>
+        <v>440</v>
       </c>
       <c r="D14" s="8">
         <f>C17</f>
@@ -6307,22 +6157,22 @@
     </row>
     <row r="32">
       <c r="B32" s="8" t="n">
-        <v>190.8</v>
+        <v>7182.7</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>349.8</v>
+        <v>13168.3</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>445.2</v>
+        <v>16759.6</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>286.2</v>
+        <v>10774</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>190.8</v>
+        <v>7182.7</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>127.2</v>
+        <v>4788.5</v>
       </c>
     </row>
     <row r="33"/>
@@ -7824,7 +7674,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>397.5</v>
+        <v>14963.9</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -7854,7 +7704,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>1192.5</v>
+        <v>44891.8</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -7884,7 +7734,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>238.5</v>
+        <v>8978.4</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -7914,7 +7764,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>636</v>
+        <v>23942.3</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
